--- a/Data/metadaten_grafiken_eidgenoessische_abstimmungen.xlsx
+++ b/Data/metadaten_grafiken_eidgenoessische_abstimmungen.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/60387dca0f89eeaf/SDA_eidgenoessische_abstimmungen/20260614_LENA_Abstimmungen/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/60387dca0f89eeaf/SDA_eidgenoessische_abstimmungen/20260927_LENA_Abstimmungen/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_C8A05664C3574AFC124848F9E2CB447E115BF177" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39418B7F-A1F6-4395-A5C4-A2CEEA499653}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="11_C8A05664C3574AFC124848F9E2CB447E115BF177" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6758811-2CB1-4264-9FFC-BB0DE4E1C1EB}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="255" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Schweiz" sheetId="1" r:id="rId1"/>
@@ -152,1207 +152,1207 @@
     <t>Kanton ZH</t>
   </si>
   <si>
-    <t>Aktueller Stand der Abstimmungen vom 14. Juni 2026</t>
-  </si>
-  <si>
-    <t>GUR9I</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/GUR9I/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="Aktueller Stand der Abstimmungen vom 14. Juni 2026" aria-label="Balken (gestapelt)" id="datawrapper-chart-GUR9I" src="https://datawrapper.dwcdn.net/GUR9I/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="469" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:469px" id="datawrapper-vis-GUR9I"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/GUR9I/embed.js" charset="utf-8" data-target="#datawrapper-vis-GUR9I"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/GUR9I/full.png?unq=keystone-sda" alt="Aktueller Stand der Abstimmungen vom 14. Juni 2026 (Balken (gestapelt))" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>Etat actuel des votes au 14 juin 2026</t>
-  </si>
-  <si>
-    <t>CWoUm</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/CWoUm/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="Etat actuel des votes au 14 juin 2026" aria-label="Barres empilées" id="datawrapper-chart-CWoUm" src="https://datawrapper.dwcdn.net/CWoUm/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="452" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:452px" id="datawrapper-vis-CWoUm"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/CWoUm/embed.js" charset="utf-8" data-target="#datawrapper-vis-CWoUm"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/CWoUm/full.png?unq=keystone-sda" alt="Etat actuel des votes au 14 juin 2026 (Barres empilées)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>Situazione attuale delle votazioni del 14 giugno 2026</t>
-  </si>
-  <si>
-    <t>tAznO</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/tAznO/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="Situazione attuale delle votazioni del 14 giugno 2026" aria-label="Barre impilate" id="datawrapper-chart-tAznO" src="https://datawrapper.dwcdn.net/tAznO/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="469" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:469px" id="datawrapper-vis-tAznO"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/tAznO/embed.js" charset="utf-8" data-target="#datawrapper-vis-tAznO"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/tAznO/full.png?unq=keystone-sda" alt="Situazione attuale delle votazioni del 14 giugno 2026 (Barre impilate)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>CH_Zuwanderung</t>
-  </si>
-  <si>
-    <t>CH_Zivildienst</t>
-  </si>
-  <si>
-    <t>Zivildienstgesetz</t>
-  </si>
-  <si>
-    <t>Zivildienstgesetz: Übersicht Kantone</t>
-  </si>
-  <si>
-    <t>Loi sur le service civil</t>
-  </si>
-  <si>
-    <t>c1ExJ</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/c1ExJ/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="Nachhaltigkeitsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-c1ExJ" src="https://datawrapper.dwcdn.net/c1ExJ/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-c1ExJ"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/c1ExJ/embed.js" charset="utf-8" data-target="#datawrapper-vis-c1ExJ"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/c1ExJ/full.png?unq=keystone-sda" alt="Nachhaltigkeitsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>DMUD9</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/DMUD9/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="Nachhaltigkeitsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-DMUD9" src="https://datawrapper.dwcdn.net/DMUD9/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="534" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:534px" id="datawrapper-vis-DMUD9"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/DMUD9/embed.js" charset="utf-8" data-target="#datawrapper-vis-DMUD9"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/DMUD9/full.png?unq=keystone-sda" alt="Nachhaltigkeitsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>ImnFI</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/ImnFI/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="Nachhaltigkeitsinitiative: Übersicht Kantone" aria-label="Tabelle" id="datawrapper-chart-ImnFI" src="https://datawrapper.dwcdn.net/ImnFI/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="1414" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:1414px" id="datawrapper-vis-ImnFI"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/ImnFI/embed.js" charset="utf-8" data-target="#datawrapper-vis-ImnFI"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/ImnFI/full.png?unq=keystone-sda" alt="Nachhaltigkeitsinitiative: Übersicht Kantone (Tabelle)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>32eia</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/32eia/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="Initiative pour la durabilité" aria-label="Carte choroplèthe" id="datawrapper-chart-32eia" src="https://datawrapper.dwcdn.net/32eia/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:495px" id="datawrapper-vis-32eia"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/32eia/embed.js" charset="utf-8" data-target="#datawrapper-vis-32eia"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/32eia/full.png?unq=keystone-sda" alt="Initiative pour la durabilité (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>zrA4T</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/zrA4T/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="Initiative pour la durabilité" aria-label="Carte choroplèthe" id="datawrapper-chart-zrA4T" src="https://datawrapper.dwcdn.net/zrA4T/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="534" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:534px" id="datawrapper-vis-zrA4T"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/zrA4T/embed.js" charset="utf-8" data-target="#datawrapper-vis-zrA4T"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/zrA4T/full.png?unq=keystone-sda" alt="Initiative pour la durabilité (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>nuIdj</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/nuIdj/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="Initiative pour la durabilité: résultats cantonaux" aria-label="Tableau" id="datawrapper-chart-nuIdj" src="https://datawrapper.dwcdn.net/nuIdj/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="1402" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:1402px" id="datawrapper-vis-nuIdj"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/nuIdj/embed.js" charset="utf-8" data-target="#datawrapper-vis-nuIdj"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/nuIdj/full.png?unq=keystone-sda" alt="Initiative pour la durabilité: résultats cantonaux (Tableau)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>iwqqq</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/iwqqq/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="Iniziativa per la sostenibilità" aria-label="Mappa coropletica" id="datawrapper-chart-iwqqq" src="https://datawrapper.dwcdn.net/iwqqq/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="534" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:534px" id="datawrapper-vis-iwqqq"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/iwqqq/embed.js" charset="utf-8" data-target="#datawrapper-vis-iwqqq"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/iwqqq/full.png?unq=keystone-sda" alt="Iniziativa per la sostenibilità (Mappa coropletica)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>mC34K</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/mC34K/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="Iniziativa per la sostenibilità" aria-label="Mappa coropletica" id="datawrapper-chart-mC34K" src="https://datawrapper.dwcdn.net/mC34K/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="534" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:534px" id="datawrapper-vis-mC34K"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/mC34K/embed.js" charset="utf-8" data-target="#datawrapper-vis-mC34K"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/mC34K/full.png?unq=keystone-sda" alt="Iniziativa per la sostenibilità (Mappa coropletica)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>LYFsr</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/LYFsr/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="Iniziativa per la sostenibilità: panoramica dei cantoni" aria-label="Tabella" id="datawrapper-chart-LYFsr" src="https://datawrapper.dwcdn.net/LYFsr/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="1402" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:1402px" id="datawrapper-vis-LYFsr"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/LYFsr/embed.js" charset="utf-8" data-target="#datawrapper-vis-LYFsr"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/LYFsr/full.png?unq=keystone-sda" alt="Iniziativa per la sostenibilità: panoramica dei cantoni (Tabella)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>9rWWe</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/9rWWe/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="Zivildienstgesetz" aria-label="Choroplethen-Karte" id="datawrapper-chart-9rWWe" src="https://datawrapper.dwcdn.net/9rWWe/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-9rWWe"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/9rWWe/embed.js" charset="utf-8" data-target="#datawrapper-vis-9rWWe"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/9rWWe/full.png?unq=keystone-sda" alt="Zivildienstgesetz (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>0xLwm</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/0xLwm/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="Zivildienstgesetz" aria-label="Choroplethen-Karte" id="datawrapper-chart-0xLwm" src="https://datawrapper.dwcdn.net/0xLwm/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="534" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:534px" id="datawrapper-vis-0xLwm"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/0xLwm/embed.js" charset="utf-8" data-target="#datawrapper-vis-0xLwm"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/0xLwm/full.png?unq=keystone-sda" alt="Zivildienstgesetz (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>vRXzs</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/vRXzs/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="Zivildienstgesetz: Übersicht Kantone" aria-label="Tabelle" id="datawrapper-chart-vRXzs" src="https://datawrapper.dwcdn.net/vRXzs/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="1414" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:1414px" id="datawrapper-vis-vRXzs"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/vRXzs/embed.js" charset="utf-8" data-target="#datawrapper-vis-vRXzs"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/vRXzs/full.png?unq=keystone-sda" alt="Zivildienstgesetz: Übersicht Kantone (Tabelle)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>6TmKd</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/6TmKd/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="Loi sur le service civil" aria-label="Carte choroplèthe" id="datawrapper-chart-6TmKd" src="https://datawrapper.dwcdn.net/6TmKd/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:495px" id="datawrapper-vis-6TmKd"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/6TmKd/embed.js" charset="utf-8" data-target="#datawrapper-vis-6TmKd"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/6TmKd/full.png?unq=keystone-sda" alt="Loi sur le service civil (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>MXpgX</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/MXpgX/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="Loi sur le service civil" aria-label="Carte choroplèthe" id="datawrapper-chart-MXpgX" src="https://datawrapper.dwcdn.net/MXpgX/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="534" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:534px" id="datawrapper-vis-MXpgX"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/MXpgX/embed.js" charset="utf-8" data-target="#datawrapper-vis-MXpgX"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/MXpgX/full.png?unq=keystone-sda" alt="Loi sur le service civil (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>Loi sur le service civil: résultats cantonaux</t>
-  </si>
-  <si>
-    <t>pfrwr</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/pfrwr/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="Loi sur le service civil: résultats cantonaux" aria-label="Tableau" id="datawrapper-chart-pfrwr" src="https://datawrapper.dwcdn.net/pfrwr/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="1402" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:1402px" id="datawrapper-vis-pfrwr"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/pfrwr/embed.js" charset="utf-8" data-target="#datawrapper-vis-pfrwr"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/pfrwr/full.png?unq=keystone-sda" alt="Loi sur le service civil: résultats cantonaux (Tableau)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>Legge sul servizio civile</t>
-  </si>
-  <si>
-    <t>CpTT3</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/CpTT3/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="Legge sul servizio civile" aria-label="Mappa coropletica" id="datawrapper-chart-CpTT3" src="https://datawrapper.dwcdn.net/CpTT3/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="534" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:534px" id="datawrapper-vis-CpTT3"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/CpTT3/embed.js" charset="utf-8" data-target="#datawrapper-vis-CpTT3"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/CpTT3/full.png?unq=keystone-sda" alt="Legge sul servizio civile (Mappa coropletica)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>6zZx0</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/6zZx0/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="Legge sul servizio civile" aria-label="Mappa coropletica" id="datawrapper-chart-6zZx0" src="https://datawrapper.dwcdn.net/6zZx0/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="534" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:534px" id="datawrapper-vis-6zZx0"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/6zZx0/embed.js" charset="utf-8" data-target="#datawrapper-vis-6zZx0"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/6zZx0/full.png?unq=keystone-sda" alt="Legge sul servizio civile (Mappa coropletica)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>Legge sul servizio civile: panoramica dei cantoni</t>
-  </si>
-  <si>
-    <t>q0QEX</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/q0QEX/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="Legge sul servizio civile: panoramica dei cantoni" aria-label="Tabella" id="datawrapper-chart-q0QEX" src="https://datawrapper.dwcdn.net/q0QEX/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="1402" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:1402px" id="datawrapper-vis-q0QEX"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/q0QEX/embed.js" charset="utf-8" data-target="#datawrapper-vis-q0QEX"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/q0QEX/full.png?unq=keystone-sda" alt="Legge sul servizio civile: panoramica dei cantoni (Tabella)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>dQYL5</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/dQYL5/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="AG: Nachhaltigkeitsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-dQYL5" src="https://datawrapper.dwcdn.net/dQYL5/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-dQYL5"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/dQYL5/embed.js" charset="utf-8" data-target="#datawrapper-vis-dQYL5"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/dQYL5/full.png?unq=keystone-sda" alt="AG: Nachhaltigkeitsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>AG: Zivildienstgesetz</t>
-  </si>
-  <si>
-    <t>Z50Rm</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/Z50Rm/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="AG: Zivildienstgesetz" aria-label="Choroplethen-Karte" id="datawrapper-chart-Z50Rm" src="https://datawrapper.dwcdn.net/Z50Rm/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-Z50Rm"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/Z50Rm/embed.js" charset="utf-8" data-target="#datawrapper-vis-Z50Rm"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/Z50Rm/full.png?unq=keystone-sda" alt="AG: Zivildienstgesetz (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>szzMD</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/szzMD/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="AI: Nachhaltigkeitsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-szzMD" src="https://datawrapper.dwcdn.net/szzMD/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-szzMD"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/szzMD/embed.js" charset="utf-8" data-target="#datawrapper-vis-szzMD"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/szzMD/full.png?unq=keystone-sda" alt="AI: Nachhaltigkeitsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>AI: Zivildienstgesetz</t>
-  </si>
-  <si>
-    <t>h1vp5</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/h1vp5/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="AI: Zivildienstgesetz" aria-label="Choroplethen-Karte" id="datawrapper-chart-h1vp5" src="https://datawrapper.dwcdn.net/h1vp5/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-h1vp5"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/h1vp5/embed.js" charset="utf-8" data-target="#datawrapper-vis-h1vp5"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/h1vp5/full.png?unq=keystone-sda" alt="AI: Zivildienstgesetz (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>QyVo3</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/QyVo3/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="AR: Nachhaltigkeitsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-QyVo3" src="https://datawrapper.dwcdn.net/QyVo3/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-QyVo3"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/QyVo3/embed.js" charset="utf-8" data-target="#datawrapper-vis-QyVo3"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/QyVo3/full.png?unq=keystone-sda" alt="AR: Nachhaltigkeitsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>AR: Zivildienstgesetz</t>
-  </si>
-  <si>
-    <t>nhAMo</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/nhAMo/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="AR: Zivildienstgesetz" aria-label="Choroplethen-Karte" id="datawrapper-chart-nhAMo" src="https://datawrapper.dwcdn.net/nhAMo/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-nhAMo"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/nhAMo/embed.js" charset="utf-8" data-target="#datawrapper-vis-nhAMo"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/nhAMo/full.png?unq=keystone-sda" alt="AR: Zivildienstgesetz (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>o7wWO</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/o7wWO/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="BE: Nachhaltigkeitsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-o7wWO" src="https://datawrapper.dwcdn.net/o7wWO/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-o7wWO"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/o7wWO/embed.js" charset="utf-8" data-target="#datawrapper-vis-o7wWO"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/o7wWO/full.png?unq=keystone-sda" alt="BE: Nachhaltigkeitsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>X02Dr</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/X02Dr/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="BE: Initiative pour la durabilité" aria-label="Carte choroplèthe" id="datawrapper-chart-X02Dr" src="https://datawrapper.dwcdn.net/X02Dr/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:495px" id="datawrapper-vis-X02Dr"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/X02Dr/embed.js" charset="utf-8" data-target="#datawrapper-vis-X02Dr"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/X02Dr/full.png?unq=keystone-sda" alt="BE: Initiative pour la durabilité (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>BE: Zivildienstgesetz</t>
-  </si>
-  <si>
-    <t>S96gf</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/S96gf/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="BE: Zivildienstgesetz" aria-label="Choroplethen-Karte" id="datawrapper-chart-S96gf" src="https://datawrapper.dwcdn.net/S96gf/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-S96gf"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/S96gf/embed.js" charset="utf-8" data-target="#datawrapper-vis-S96gf"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/S96gf/full.png?unq=keystone-sda" alt="BE: Zivildienstgesetz (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>BE: Loi sur le service civil</t>
-  </si>
-  <si>
-    <t>Tt81J</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/Tt81J/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="BE: Loi sur le service civil" aria-label="Carte choroplèthe" id="datawrapper-chart-Tt81J" src="https://datawrapper.dwcdn.net/Tt81J/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:495px" id="datawrapper-vis-Tt81J"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/Tt81J/embed.js" charset="utf-8" data-target="#datawrapper-vis-Tt81J"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/Tt81J/full.png?unq=keystone-sda" alt="BE: Loi sur le service civil (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>7OOKG</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/7OOKG/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="BL: Nachhaltigkeitsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-7OOKG" src="https://datawrapper.dwcdn.net/7OOKG/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-7OOKG"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/7OOKG/embed.js" charset="utf-8" data-target="#datawrapper-vis-7OOKG"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/7OOKG/full.png?unq=keystone-sda" alt="BL: Nachhaltigkeitsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>BL: Zivildienstgesetz</t>
-  </si>
-  <si>
-    <t>1JKWC</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/1JKWC/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="BL: Zivildienstgesetz" aria-label="Choroplethen-Karte" id="datawrapper-chart-1JKWC" src="https://datawrapper.dwcdn.net/1JKWC/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-1JKWC"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/1JKWC/embed.js" charset="utf-8" data-target="#datawrapper-vis-1JKWC"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/1JKWC/full.png?unq=keystone-sda" alt="BL: Zivildienstgesetz (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>ygje0</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/ygje0/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="BS: Nachhaltigkeitsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-ygje0" src="https://datawrapper.dwcdn.net/ygje0/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-ygje0"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/ygje0/embed.js" charset="utf-8" data-target="#datawrapper-vis-ygje0"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/ygje0/full.png?unq=keystone-sda" alt="BS: Nachhaltigkeitsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>BS: Zivildienstgesetz</t>
-  </si>
-  <si>
-    <t>GTE0i</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/GTE0i/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="BS: Zivildienstgesetz" aria-label="Choroplethen-Karte" id="datawrapper-chart-GTE0i" src="https://datawrapper.dwcdn.net/GTE0i/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-GTE0i"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/GTE0i/embed.js" charset="utf-8" data-target="#datawrapper-vis-GTE0i"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/GTE0i/full.png?unq=keystone-sda" alt="BS: Zivildienstgesetz (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>2EhHC</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/2EhHC/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="FR: Nachhaltigkeitsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-2EhHC" src="https://datawrapper.dwcdn.net/2EhHC/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-2EhHC"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/2EhHC/embed.js" charset="utf-8" data-target="#datawrapper-vis-2EhHC"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/2EhHC/full.png?unq=keystone-sda" alt="FR: Nachhaltigkeitsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>VAcnk</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/VAcnk/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="FR: Initiative pour la durabilité" aria-label="Carte choroplèthe" id="datawrapper-chart-VAcnk" src="https://datawrapper.dwcdn.net/VAcnk/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:495px" id="datawrapper-vis-VAcnk"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/VAcnk/embed.js" charset="utf-8" data-target="#datawrapper-vis-VAcnk"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/VAcnk/full.png?unq=keystone-sda" alt="FR: Initiative pour la durabilité (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>FR: Zivildienstgesetz</t>
-  </si>
-  <si>
-    <t>XCgHL</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/XCgHL/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="FR: Zivildienstgesetz" aria-label="Choroplethen-Karte" id="datawrapper-chart-XCgHL" src="https://datawrapper.dwcdn.net/XCgHL/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-XCgHL"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/XCgHL/embed.js" charset="utf-8" data-target="#datawrapper-vis-XCgHL"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/XCgHL/full.png?unq=keystone-sda" alt="FR: Zivildienstgesetz (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>FR: Loi sur le service civil</t>
-  </si>
-  <si>
-    <t>GcOag</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/GcOag/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="FR: Loi sur le service civil" aria-label="Carte choroplèthe" id="datawrapper-chart-GcOag" src="https://datawrapper.dwcdn.net/GcOag/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:495px" id="datawrapper-vis-GcOag"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/GcOag/embed.js" charset="utf-8" data-target="#datawrapper-vis-GcOag"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/GcOag/full.png?unq=keystone-sda" alt="FR: Loi sur le service civil (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>H5ZIT</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/H5ZIT/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="GE: Initiative pour la durabilité" aria-label="Carte choroplèthe" id="datawrapper-chart-H5ZIT" src="https://datawrapper.dwcdn.net/H5ZIT/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:495px" id="datawrapper-vis-H5ZIT"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/H5ZIT/embed.js" charset="utf-8" data-target="#datawrapper-vis-H5ZIT"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/H5ZIT/full.png?unq=keystone-sda" alt="GE: Initiative pour la durabilité (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>GE: Loi sur le service civil</t>
-  </si>
-  <si>
-    <t>D0frM</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/D0frM/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="GE: Loi sur le service civil" aria-label="Carte choroplèthe" id="datawrapper-chart-D0frM" src="https://datawrapper.dwcdn.net/D0frM/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:495px" id="datawrapper-vis-D0frM"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/D0frM/embed.js" charset="utf-8" data-target="#datawrapper-vis-D0frM"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/D0frM/full.png?unq=keystone-sda" alt="GE: Loi sur le service civil (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>mzMH6</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/mzMH6/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="GL: Nachhaltigkeitsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-mzMH6" src="https://datawrapper.dwcdn.net/mzMH6/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-mzMH6"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/mzMH6/embed.js" charset="utf-8" data-target="#datawrapper-vis-mzMH6"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/mzMH6/full.png?unq=keystone-sda" alt="GL: Nachhaltigkeitsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>GL: Zivildienstgesetz</t>
-  </si>
-  <si>
-    <t>Fmijr</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/Fmijr/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="GL: Zivildienstgesetz" aria-label="Choroplethen-Karte" id="datawrapper-chart-Fmijr" src="https://datawrapper.dwcdn.net/Fmijr/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-Fmijr"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/Fmijr/embed.js" charset="utf-8" data-target="#datawrapper-vis-Fmijr"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/Fmijr/full.png?unq=keystone-sda" alt="GL: Zivildienstgesetz (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>3x8EC</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/3x8EC/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="GR: Nachhaltigkeitsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-3x8EC" src="https://datawrapper.dwcdn.net/3x8EC/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-3x8EC"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/3x8EC/embed.js" charset="utf-8" data-target="#datawrapper-vis-3x8EC"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/3x8EC/full.png?unq=keystone-sda" alt="GR: Nachhaltigkeitsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>TmruB</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/TmruB/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="GR: Iniziativa per la sostenibilità" aria-label="Mappa coropletica" id="datawrapper-chart-TmruB" src="https://datawrapper.dwcdn.net/TmruB/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="534" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:534px" id="datawrapper-vis-TmruB"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/TmruB/embed.js" charset="utf-8" data-target="#datawrapper-vis-TmruB"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/TmruB/full.png?unq=keystone-sda" alt="GR: Iniziativa per la sostenibilità (Mappa coropletica)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>GR: Zivildienstgesetz</t>
-  </si>
-  <si>
-    <t>RHRTV</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/RHRTV/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="GR: Zivildienstgesetz" aria-label="Choroplethen-Karte" id="datawrapper-chart-RHRTV" src="https://datawrapper.dwcdn.net/RHRTV/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-RHRTV"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/RHRTV/embed.js" charset="utf-8" data-target="#datawrapper-vis-RHRTV"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/RHRTV/full.png?unq=keystone-sda" alt="GR: Zivildienstgesetz (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>GR: Legge sul servizio civile</t>
-  </si>
-  <si>
-    <t>T84sf</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/T84sf/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="GR: Legge sul servizio civile" aria-label="Mappa coropletica" id="datawrapper-chart-T84sf" src="https://datawrapper.dwcdn.net/T84sf/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="534" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:534px" id="datawrapper-vis-T84sf"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/T84sf/embed.js" charset="utf-8" data-target="#datawrapper-vis-T84sf"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/T84sf/full.png?unq=keystone-sda" alt="GR: Legge sul servizio civile (Mappa coropletica)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>G37SQ</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/G37SQ/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="JU: Initiative pour la durabilité" aria-label="Carte choroplèthe" id="datawrapper-chart-G37SQ" src="https://datawrapper.dwcdn.net/G37SQ/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:495px" id="datawrapper-vis-G37SQ"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/G37SQ/embed.js" charset="utf-8" data-target="#datawrapper-vis-G37SQ"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/G37SQ/full.png?unq=keystone-sda" alt="JU: Initiative pour la durabilité (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>JU: Loi sur le service civil</t>
-  </si>
-  <si>
-    <t>WgMEI</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/WgMEI/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="JU: Loi sur le service civil" aria-label="Carte choroplèthe" id="datawrapper-chart-WgMEI" src="https://datawrapper.dwcdn.net/WgMEI/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:495px" id="datawrapper-vis-WgMEI"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/WgMEI/embed.js" charset="utf-8" data-target="#datawrapper-vis-WgMEI"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/WgMEI/full.png?unq=keystone-sda" alt="JU: Loi sur le service civil (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>SwR7b</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/SwR7b/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="LU: Nachhaltigkeitsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-SwR7b" src="https://datawrapper.dwcdn.net/SwR7b/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-SwR7b"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/SwR7b/embed.js" charset="utf-8" data-target="#datawrapper-vis-SwR7b"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/SwR7b/full.png?unq=keystone-sda" alt="LU: Nachhaltigkeitsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>LU: Zivildienstgesetz</t>
-  </si>
-  <si>
-    <t>anLJA</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/anLJA/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="LU: Zivildienstgesetz" aria-label="Choroplethen-Karte" id="datawrapper-chart-anLJA" src="https://datawrapper.dwcdn.net/anLJA/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-anLJA"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/anLJA/embed.js" charset="utf-8" data-target="#datawrapper-vis-anLJA"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/anLJA/full.png?unq=keystone-sda" alt="LU: Zivildienstgesetz (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>8QeID</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/8QeID/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="NE: Initiative pour la durabilité" aria-label="Carte choroplèthe" id="datawrapper-chart-8QeID" src="https://datawrapper.dwcdn.net/8QeID/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:495px" id="datawrapper-vis-8QeID"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/8QeID/embed.js" charset="utf-8" data-target="#datawrapper-vis-8QeID"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/8QeID/full.png?unq=keystone-sda" alt="NE: Initiative pour la durabilité (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>NE: Loi sur le service civil</t>
-  </si>
-  <si>
-    <t>7K5Js</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/7K5Js/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="NE: Loi sur le service civil" aria-label="Carte choroplèthe" id="datawrapper-chart-7K5Js" src="https://datawrapper.dwcdn.net/7K5Js/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:495px" id="datawrapper-vis-7K5Js"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/7K5Js/embed.js" charset="utf-8" data-target="#datawrapper-vis-7K5Js"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/7K5Js/full.png?unq=keystone-sda" alt="NE: Loi sur le service civil (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>u1SLr</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/u1SLr/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="NW: Nachhaltigkeitsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-u1SLr" src="https://datawrapper.dwcdn.net/u1SLr/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-u1SLr"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/u1SLr/embed.js" charset="utf-8" data-target="#datawrapper-vis-u1SLr"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/u1SLr/full.png?unq=keystone-sda" alt="NW: Nachhaltigkeitsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>NW: Zivildienstgesetz</t>
-  </si>
-  <si>
-    <t>HiJcP</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/HiJcP/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="NW: Zivildienstgesetz" aria-label="Choroplethen-Karte" id="datawrapper-chart-HiJcP" src="https://datawrapper.dwcdn.net/HiJcP/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-HiJcP"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/HiJcP/embed.js" charset="utf-8" data-target="#datawrapper-vis-HiJcP"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/HiJcP/full.png?unq=keystone-sda" alt="NW: Zivildienstgesetz (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>qcxYU</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/qcxYU/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="OW: Nachhaltigkeitsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-qcxYU" src="https://datawrapper.dwcdn.net/qcxYU/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-qcxYU"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/qcxYU/embed.js" charset="utf-8" data-target="#datawrapper-vis-qcxYU"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/qcxYU/full.png?unq=keystone-sda" alt="OW: Nachhaltigkeitsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>OW: Zivildienstgesetz</t>
-  </si>
-  <si>
-    <t>fOhhk</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/fOhhk/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="OW: Zivildienstgesetz" aria-label="Choroplethen-Karte" id="datawrapper-chart-fOhhk" src="https://datawrapper.dwcdn.net/fOhhk/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-fOhhk"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/fOhhk/embed.js" charset="utf-8" data-target="#datawrapper-vis-fOhhk"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/fOhhk/full.png?unq=keystone-sda" alt="OW: Zivildienstgesetz (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>aahBg</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/aahBg/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="SG: Nachhaltigkeitsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-aahBg" src="https://datawrapper.dwcdn.net/aahBg/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-aahBg"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/aahBg/embed.js" charset="utf-8" data-target="#datawrapper-vis-aahBg"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/aahBg/full.png?unq=keystone-sda" alt="SG: Nachhaltigkeitsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>SG: Zivildienstgesetz</t>
-  </si>
-  <si>
-    <t>coyQ6</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/coyQ6/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="SG: Zivildienstgesetz" aria-label="Choroplethen-Karte" id="datawrapper-chart-coyQ6" src="https://datawrapper.dwcdn.net/coyQ6/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-coyQ6"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/coyQ6/embed.js" charset="utf-8" data-target="#datawrapper-vis-coyQ6"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/coyQ6/full.png?unq=keystone-sda" alt="SG: Zivildienstgesetz (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>BkkSu</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/BkkSu/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="SH: Nachhaltigkeitsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-BkkSu" src="https://datawrapper.dwcdn.net/BkkSu/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-BkkSu"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/BkkSu/embed.js" charset="utf-8" data-target="#datawrapper-vis-BkkSu"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/BkkSu/full.png?unq=keystone-sda" alt="SH: Nachhaltigkeitsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>SH: Zivildienstgesetz</t>
-  </si>
-  <si>
-    <t>dB3gj</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/dB3gj/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="SH: Zivildienstgesetz" aria-label="Choroplethen-Karte" id="datawrapper-chart-dB3gj" src="https://datawrapper.dwcdn.net/dB3gj/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-dB3gj"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/dB3gj/embed.js" charset="utf-8" data-target="#datawrapper-vis-dB3gj"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/dB3gj/full.png?unq=keystone-sda" alt="SH: Zivildienstgesetz (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>veYEI</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/veYEI/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="SO: Nachhaltigkeitsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-veYEI" src="https://datawrapper.dwcdn.net/veYEI/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-veYEI"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/veYEI/embed.js" charset="utf-8" data-target="#datawrapper-vis-veYEI"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/veYEI/full.png?unq=keystone-sda" alt="SO: Nachhaltigkeitsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>SO: Zivildienstgesetz</t>
-  </si>
-  <si>
-    <t>eNLbr</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/eNLbr/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="SO: Zivildienstgesetz" aria-label="Choroplethen-Karte" id="datawrapper-chart-eNLbr" src="https://datawrapper.dwcdn.net/eNLbr/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-eNLbr"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/eNLbr/embed.js" charset="utf-8" data-target="#datawrapper-vis-eNLbr"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/eNLbr/full.png?unq=keystone-sda" alt="SO: Zivildienstgesetz (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>gPdn9</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/gPdn9/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="SZ: Nachhaltigkeitsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-gPdn9" src="https://datawrapper.dwcdn.net/gPdn9/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-gPdn9"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/gPdn9/embed.js" charset="utf-8" data-target="#datawrapper-vis-gPdn9"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/gPdn9/full.png?unq=keystone-sda" alt="SZ: Nachhaltigkeitsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>SZ: Zivildienstgesetz</t>
-  </si>
-  <si>
-    <t>CzsEm</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/CzsEm/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="SZ: Zivildienstgesetz" aria-label="Choroplethen-Karte" id="datawrapper-chart-CzsEm" src="https://datawrapper.dwcdn.net/CzsEm/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-CzsEm"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/CzsEm/embed.js" charset="utf-8" data-target="#datawrapper-vis-CzsEm"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/CzsEm/full.png?unq=keystone-sda" alt="SZ: Zivildienstgesetz (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>wflfh</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/wflfh/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="TG: Nachhaltigkeitsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-wflfh" src="https://datawrapper.dwcdn.net/wflfh/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-wflfh"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/wflfh/embed.js" charset="utf-8" data-target="#datawrapper-vis-wflfh"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/wflfh/full.png?unq=keystone-sda" alt="TG: Nachhaltigkeitsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>TG: Zivildienstgesetz</t>
-  </si>
-  <si>
-    <t>ovSTX</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/ovSTX/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="TG: Zivildienstgesetz" aria-label="Choroplethen-Karte" id="datawrapper-chart-ovSTX" src="https://datawrapper.dwcdn.net/ovSTX/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-ovSTX"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/ovSTX/embed.js" charset="utf-8" data-target="#datawrapper-vis-ovSTX"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/ovSTX/full.png?unq=keystone-sda" alt="TG: Zivildienstgesetz (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>rBnpN</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/rBnpN/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="TI: Iniziativa per la sostenibilità" aria-label="Mappa coropletica" id="datawrapper-chart-rBnpN" src="https://datawrapper.dwcdn.net/rBnpN/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="534" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:534px" id="datawrapper-vis-rBnpN"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/rBnpN/embed.js" charset="utf-8" data-target="#datawrapper-vis-rBnpN"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/rBnpN/full.png?unq=keystone-sda" alt="TI: Iniziativa per la sostenibilità (Mappa coropletica)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>TI: Legge sul servizio civile</t>
-  </si>
-  <si>
-    <t>lrCXZ</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/lrCXZ/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="TI: Legge sul servizio civile" aria-label="Mappa coropletica" id="datawrapper-chart-lrCXZ" src="https://datawrapper.dwcdn.net/lrCXZ/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="534" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:534px" id="datawrapper-vis-lrCXZ"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/lrCXZ/embed.js" charset="utf-8" data-target="#datawrapper-vis-lrCXZ"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/lrCXZ/full.png?unq=keystone-sda" alt="TI: Legge sul servizio civile (Mappa coropletica)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>7Hr3X</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/7Hr3X/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="UR: Nachhaltigkeitsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-7Hr3X" src="https://datawrapper.dwcdn.net/7Hr3X/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-7Hr3X"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/7Hr3X/embed.js" charset="utf-8" data-target="#datawrapper-vis-7Hr3X"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/7Hr3X/full.png?unq=keystone-sda" alt="UR: Nachhaltigkeitsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>UR: Zivildienstgesetz</t>
-  </si>
-  <si>
-    <t>6cpOC</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/6cpOC/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="UR: Zivildienstgesetz" aria-label="Choroplethen-Karte" id="datawrapper-chart-6cpOC" src="https://datawrapper.dwcdn.net/6cpOC/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-6cpOC"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/6cpOC/embed.js" charset="utf-8" data-target="#datawrapper-vis-6cpOC"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/6cpOC/full.png?unq=keystone-sda" alt="UR: Zivildienstgesetz (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>hlym2</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/hlym2/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="VD: Initiative pour la durabilité" aria-label="Carte choroplèthe" id="datawrapper-chart-hlym2" src="https://datawrapper.dwcdn.net/hlym2/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:495px" id="datawrapper-vis-hlym2"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/hlym2/embed.js" charset="utf-8" data-target="#datawrapper-vis-hlym2"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/hlym2/full.png?unq=keystone-sda" alt="VD: Initiative pour la durabilité (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>VD: Loi sur le service civil</t>
-  </si>
-  <si>
-    <t>7NkPg</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/7NkPg/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="VD: Loi sur le service civil" aria-label="Carte choroplèthe" id="datawrapper-chart-7NkPg" src="https://datawrapper.dwcdn.net/7NkPg/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:495px" id="datawrapper-vis-7NkPg"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/7NkPg/embed.js" charset="utf-8" data-target="#datawrapper-vis-7NkPg"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/7NkPg/full.png?unq=keystone-sda" alt="VD: Loi sur le service civil (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>vSdku</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/vSdku/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="VS: Nachhaltigkeitsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-vSdku" src="https://datawrapper.dwcdn.net/vSdku/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-vSdku"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/vSdku/embed.js" charset="utf-8" data-target="#datawrapper-vis-vSdku"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/vSdku/full.png?unq=keystone-sda" alt="VS: Nachhaltigkeitsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>qQVp6</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/qQVp6/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="VS: Initiative pour la durabilité" aria-label="Carte choroplèthe" id="datawrapper-chart-qQVp6" src="https://datawrapper.dwcdn.net/qQVp6/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:495px" id="datawrapper-vis-qQVp6"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/qQVp6/embed.js" charset="utf-8" data-target="#datawrapper-vis-qQVp6"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/qQVp6/full.png?unq=keystone-sda" alt="VS: Initiative pour la durabilité (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>VS: Zivildienstgesetz</t>
-  </si>
-  <si>
-    <t>HLp1y</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/HLp1y/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="VS: Zivildienstgesetz" aria-label="Choroplethen-Karte" id="datawrapper-chart-HLp1y" src="https://datawrapper.dwcdn.net/HLp1y/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-HLp1y"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/HLp1y/embed.js" charset="utf-8" data-target="#datawrapper-vis-HLp1y"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/HLp1y/full.png?unq=keystone-sda" alt="VS: Zivildienstgesetz (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>VS: Loi sur le service civil</t>
-  </si>
-  <si>
-    <t>3No5k</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/3No5k/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="VS: Loi sur le service civil" aria-label="Carte choroplèthe" id="datawrapper-chart-3No5k" src="https://datawrapper.dwcdn.net/3No5k/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:495px" id="datawrapper-vis-3No5k"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/3No5k/embed.js" charset="utf-8" data-target="#datawrapper-vis-3No5k"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/3No5k/full.png?unq=keystone-sda" alt="VS: Loi sur le service civil (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>GuFAM</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/GuFAM/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="ZG: Nachhaltigkeitsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-GuFAM" src="https://datawrapper.dwcdn.net/GuFAM/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-GuFAM"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/GuFAM/embed.js" charset="utf-8" data-target="#datawrapper-vis-GuFAM"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/GuFAM/full.png?unq=keystone-sda" alt="ZG: Nachhaltigkeitsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>ZG: Zivildienstgesetz</t>
-  </si>
-  <si>
-    <t>XGgbK</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/XGgbK/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="ZG: Zivildienstgesetz" aria-label="Choroplethen-Karte" id="datawrapper-chart-XGgbK" src="https://datawrapper.dwcdn.net/XGgbK/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-XGgbK"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/XGgbK/embed.js" charset="utf-8" data-target="#datawrapper-vis-XGgbK"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/XGgbK/full.png?unq=keystone-sda" alt="ZG: Zivildienstgesetz (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>EbRVF</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/EbRVF/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="ZH: Nachhaltigkeitsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-EbRVF" src="https://datawrapper.dwcdn.net/EbRVF/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-EbRVF"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/EbRVF/embed.js" charset="utf-8" data-target="#datawrapper-vis-EbRVF"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/EbRVF/full.png?unq=keystone-sda" alt="ZH: Nachhaltigkeitsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>ZH: Zivildienstgesetz</t>
-  </si>
-  <si>
-    <t>i9q0m</t>
-  </si>
-  <si>
-    <t>https://datawrapper.dwcdn.net/i9q0m/1/</t>
-  </si>
-  <si>
-    <t>&lt;iframe title="ZH: Zivildienstgesetz" aria-label="Choroplethen-Karte" id="datawrapper-chart-i9q0m" src="https://datawrapper.dwcdn.net/i9q0m/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="494" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;window.addEventListener("message",function(a){if(void 0!==a.data["datawrapper-height"]){var e=document.querySelectorAll("iframe");for(var t in a.data["datawrapper-height"])for(var r,i=0;r=e[i];i++)if(r.contentWindow===a.source){var d=a.data["datawrapper-height"][t]+"px";r.style.height=d}}});&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div style="min-height:494px" id="datawrapper-vis-i9q0m"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/i9q0m/embed.js" charset="utf-8" data-target="#datawrapper-vis-i9q0m"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/i9q0m/full.png?unq=keystone-sda" alt="ZH: Zivildienstgesetz (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>Initiative "Keine 10-Millionen-Schweiz"</t>
-  </si>
-  <si>
-    <t>Initiative "Keine 10-Millionen-Schweiz": Übersicht Kantone</t>
-  </si>
-  <si>
-    <t>AG: Initiative "Keine 10-Millionen-Schweiz"</t>
-  </si>
-  <si>
-    <t>AI: Initiative "Keine 10-Millionen-Schweiz"</t>
-  </si>
-  <si>
-    <t>AR: Initiative "Keine 10-Millionen-Schweiz"</t>
-  </si>
-  <si>
-    <t>BE: Initiative "Keine 10-Millionen-Schweiz"</t>
-  </si>
-  <si>
-    <t>BL: Initiative "Keine 10-Millionen-Schweiz"</t>
-  </si>
-  <si>
-    <t>BS: Initiative "Keine 10-Millionen-Schweiz"</t>
-  </si>
-  <si>
-    <t>FR: Initiative "Keine 10-Millionen-Schweiz"</t>
-  </si>
-  <si>
-    <t>GL: Initiative "Keine 10-Millionen-Schweiz"</t>
-  </si>
-  <si>
-    <t>GR: Initiative "Keine 10-Millionen-Schweiz"</t>
-  </si>
-  <si>
-    <t>LU: Initiative "Keine 10-Millionen-Schweiz"</t>
-  </si>
-  <si>
-    <t>NW: Initiative "Keine 10-Millionen-Schweiz"</t>
-  </si>
-  <si>
-    <t>OW: Initiative "Keine 10-Millionen-Schweiz"</t>
-  </si>
-  <si>
-    <t>SG: Initiative "Keine 10-Millionen-Schweiz"</t>
-  </si>
-  <si>
-    <t>SH: Initiative "Keine 10-Millionen-Schweiz"</t>
-  </si>
-  <si>
-    <t>SO: Initiative "Keine 10-Millionen-Schweiz"</t>
-  </si>
-  <si>
-    <t>SZ: Initiative "Keine 10-Millionen-Schweiz"</t>
-  </si>
-  <si>
-    <t>TG: Initiative "Keine 10-Millionen-Schweiz"</t>
-  </si>
-  <si>
-    <t>UR: Initiative "Keine 10-Millionen-Schweiz"</t>
-  </si>
-  <si>
-    <t>VS: Initiative "Keine 10-Millionen-Schweiz"</t>
-  </si>
-  <si>
-    <t>ZG: Initiative "Keine 10-Millionen-Schweiz"</t>
-  </si>
-  <si>
-    <t>ZH: Initiative "Keine 10-Millionen-Schweiz"</t>
-  </si>
-  <si>
-    <t>Initiative "Pas de Suisse à 10 millions"</t>
-  </si>
-  <si>
-    <t>Initiative "Pas de Suisse à 10 millions": résultats cantonaux</t>
-  </si>
-  <si>
-    <t>BE: Initiative "Pas de Suisse à 10 millions"</t>
-  </si>
-  <si>
-    <t>FR: Initiative "Pas de Suisse à 10 millions"</t>
-  </si>
-  <si>
-    <t>GE: Initiative "Pas de Suisse à 10 millions"</t>
-  </si>
-  <si>
-    <t>JU: Initiative "Pas de Suisse à 10 millions"</t>
-  </si>
-  <si>
-    <t>NE: Initiative "Pas de Suisse à 10 millions"</t>
-  </si>
-  <si>
-    <t>VD: Initiative "Pas de Suisse à 10 millions"</t>
-  </si>
-  <si>
-    <t>VS: Initiative "Pas de Suisse à 10 millions"</t>
-  </si>
-  <si>
-    <t>Iniziativa "No a une Svizzera da 10 milioni"</t>
-  </si>
-  <si>
-    <t>Iniziativa "No a une Svizzera da 10 milioni": panoramica dei cantoni</t>
-  </si>
-  <si>
-    <t>GR: Iniziativa "No a une Svizzera da 10 milioni"</t>
-  </si>
-  <si>
-    <t>TI: Iniziativa "No a une Svizzera da 10 milioni"</t>
+    <t>Aktueller Stand der Abstimmungen vom 27. September 2026</t>
+  </si>
+  <si>
+    <t>eXKLM</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/eXKLM/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="Aktueller Stand der Abstimmungen vom 27. September 2026" aria-label="Balken (gestapelt)" id="datawrapper-chart-eXKLM" src="https://datawrapper.dwcdn.net/eXKLM/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="469" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:469px" id="datawrapper-vis-eXKLM"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/eXKLM/embed.js" charset="utf-8" data-target="#datawrapper-vis-eXKLM"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/eXKLM/full.png?unq=keystone-sda" alt="Aktueller Stand der Abstimmungen vom 27. September 2026 (Balken (gestapelt))" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>Etat actuel des votes au 27 septembre 2026</t>
+  </si>
+  <si>
+    <t>N1Jc1</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/N1Jc1/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="Etat actuel des votes au 27 septembre 2026" aria-label="Barres empilées" id="datawrapper-chart-N1Jc1" src="https://datawrapper.dwcdn.net/N1Jc1/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="452" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:452px" id="datawrapper-vis-N1Jc1"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/N1Jc1/embed.js" charset="utf-8" data-target="#datawrapper-vis-N1Jc1"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/N1Jc1/full.png?unq=keystone-sda" alt="Etat actuel des votes au 27 septembre 2026 (Barres empilées)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>Situazione attuale delle votazioni del 27 settembre 2026</t>
+  </si>
+  <si>
+    <t>CFOUa</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/CFOUa/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="Situazione attuale delle votazioni del 27 settembre 2026" aria-label="Barre impilate" id="datawrapper-chart-CFOUa" src="https://datawrapper.dwcdn.net/CFOUa/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="469" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:469px" id="datawrapper-vis-CFOUa"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/CFOUa/embed.js" charset="utf-8" data-target="#datawrapper-vis-CFOUa"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/CFOUa/full.png?unq=keystone-sda" alt="Situazione attuale delle votazioni del 27 settembre 2026 (Barre impilate)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>CH_Neutralitaet</t>
+  </si>
+  <si>
+    <t>Neutralitätsinitiative</t>
+  </si>
+  <si>
+    <t>sIvba</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/sIvba/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="Neutralitätsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-sIvba" src="https://datawrapper.dwcdn.net/sIvba/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-sIvba"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/sIvba/embed.js" charset="utf-8" data-target="#datawrapper-vis-sIvba"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/sIvba/full.png?unq=keystone-sda" alt="Neutralitätsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>HgQQ1</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/HgQQ1/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="Neutralitätsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-HgQQ1" src="https://datawrapper.dwcdn.net/HgQQ1/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="515" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:515px" id="datawrapper-vis-HgQQ1"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/HgQQ1/embed.js" charset="utf-8" data-target="#datawrapper-vis-HgQQ1"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/HgQQ1/full.png?unq=keystone-sda" alt="Neutralitätsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>Neutralitätsinitiative: Übersicht Kantone</t>
+  </si>
+  <si>
+    <t>5S0Wr</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/5S0Wr/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="Neutralitätsinitiative: Übersicht Kantone" aria-label="Tabelle" id="datawrapper-chart-5S0Wr" src="https://datawrapper.dwcdn.net/5S0Wr/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="1414" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:1414px" id="datawrapper-vis-5S0Wr"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/5S0Wr/embed.js" charset="utf-8" data-target="#datawrapper-vis-5S0Wr"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/5S0Wr/full.png?unq=keystone-sda" alt="Neutralitätsinitiative: Übersicht Kantone (Tabelle)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>Initiative sur la neutralité</t>
+  </si>
+  <si>
+    <t>XvsEK</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/XvsEK/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="Initiative sur la neutralité" aria-label="Carte choroplèthe" id="datawrapper-chart-XvsEK" src="https://datawrapper.dwcdn.net/XvsEK/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-XvsEK"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/XvsEK/embed.js" charset="utf-8" data-target="#datawrapper-vis-XvsEK"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/XvsEK/full.png?unq=keystone-sda" alt="Initiative sur la neutralité (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>fHbf3</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/fHbf3/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="Initiative sur la neutralité" aria-label="Carte choroplèthe" id="datawrapper-chart-fHbf3" src="https://datawrapper.dwcdn.net/fHbf3/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="515" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:515px" id="datawrapper-vis-fHbf3"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/fHbf3/embed.js" charset="utf-8" data-target="#datawrapper-vis-fHbf3"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/fHbf3/full.png?unq=keystone-sda" alt="Initiative sur la neutralité (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>Initiative sur la neutralité: résultats cantonaux</t>
+  </si>
+  <si>
+    <t>776EK</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/776EK/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="Initiative sur la neutralité: résultats cantonaux" aria-label="Tableau" id="datawrapper-chart-776EK" src="https://datawrapper.dwcdn.net/776EK/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="1402" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:1402px" id="datawrapper-vis-776EK"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/776EK/embed.js" charset="utf-8" data-target="#datawrapper-vis-776EK"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/776EK/full.png?unq=keystone-sda" alt="Initiative sur la neutralité: résultats cantonaux (Tableau)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>Iniziativa sulla neutralità</t>
+  </si>
+  <si>
+    <t>EPg6C</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/EPg6C/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="Iniziativa sulla neutralità" aria-label="Mappa coropletica" id="datawrapper-chart-EPg6C" src="https://datawrapper.dwcdn.net/EPg6C/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="515" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:515px" id="datawrapper-vis-EPg6C"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/EPg6C/embed.js" charset="utf-8" data-target="#datawrapper-vis-EPg6C"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/EPg6C/full.png?unq=keystone-sda" alt="Iniziativa sulla neutralità (Mappa coropletica)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>e7IEr</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/e7IEr/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="Iniziativa sulla neutralità" aria-label="Mappa coropletica" id="datawrapper-chart-e7IEr" src="https://datawrapper.dwcdn.net/e7IEr/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="515" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:515px" id="datawrapper-vis-e7IEr"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/e7IEr/embed.js" charset="utf-8" data-target="#datawrapper-vis-e7IEr"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/e7IEr/full.png?unq=keystone-sda" alt="Iniziativa sulla neutralità (Mappa coropletica)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>Iniziativa sulla neutralità: panoramica dei cantoni</t>
+  </si>
+  <si>
+    <t>HCavX</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/HCavX/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="Iniziativa sulla neutralità: panoramica dei cantoni" aria-label="Tabella" id="datawrapper-chart-HCavX" src="https://datawrapper.dwcdn.net/HCavX/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="1402" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:1402px" id="datawrapper-vis-HCavX"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/HCavX/embed.js" charset="utf-8" data-target="#datawrapper-vis-HCavX"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/HCavX/full.png?unq=keystone-sda" alt="Iniziativa sulla neutralità: panoramica dei cantoni (Tabella)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>CH_Ernaehrung</t>
+  </si>
+  <si>
+    <t>Ernährungsinitiative</t>
+  </si>
+  <si>
+    <t>zxrLE</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/zxrLE/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="Ernährungsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-zxrLE" src="https://datawrapper.dwcdn.net/zxrLE/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-zxrLE"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/zxrLE/embed.js" charset="utf-8" data-target="#datawrapper-vis-zxrLE"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/zxrLE/full.png?unq=keystone-sda" alt="Ernährungsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>ft0r6</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/ft0r6/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="Ernährungsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-ft0r6" src="https://datawrapper.dwcdn.net/ft0r6/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="515" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:515px" id="datawrapper-vis-ft0r6"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/ft0r6/embed.js" charset="utf-8" data-target="#datawrapper-vis-ft0r6"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/ft0r6/full.png?unq=keystone-sda" alt="Ernährungsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>Ernährungsinitiative: Übersicht Kantone</t>
+  </si>
+  <si>
+    <t>DorK2</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/DorK2/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="Ernährungsinitiative: Übersicht Kantone" aria-label="Tabelle" id="datawrapper-chart-DorK2" src="https://datawrapper.dwcdn.net/DorK2/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="1414" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:1414px" id="datawrapper-vis-DorK2"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/DorK2/embed.js" charset="utf-8" data-target="#datawrapper-vis-DorK2"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/DorK2/full.png?unq=keystone-sda" alt="Ernährungsinitiative: Übersicht Kantone (Tabelle)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>Initiative sur l'alimentation</t>
+  </si>
+  <si>
+    <t>5yShZ</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/5yShZ/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="Initiative sur l'alimentation" aria-label="Carte choroplèthe" id="datawrapper-chart-5yShZ" src="https://datawrapper.dwcdn.net/5yShZ/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-5yShZ"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/5yShZ/embed.js" charset="utf-8" data-target="#datawrapper-vis-5yShZ"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/5yShZ/full.png?unq=keystone-sda" alt="Initiative sur l'alimentation (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>7bC85</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/7bC85/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="Initiative sur l'alimentation" aria-label="Carte choroplèthe" id="datawrapper-chart-7bC85" src="https://datawrapper.dwcdn.net/7bC85/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="515" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:515px" id="datawrapper-vis-7bC85"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/7bC85/embed.js" charset="utf-8" data-target="#datawrapper-vis-7bC85"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/7bC85/full.png?unq=keystone-sda" alt="Initiative sur l'alimentation (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>Initiative sur l'alimentation: résultats cantonaux</t>
+  </si>
+  <si>
+    <t>Rj6rl</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/Rj6rl/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="Initiative sur l'alimentation: résultats cantonaux" aria-label="Tableau" id="datawrapper-chart-Rj6rl" src="https://datawrapper.dwcdn.net/Rj6rl/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="1402" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:1402px" id="datawrapper-vis-Rj6rl"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/Rj6rl/embed.js" charset="utf-8" data-target="#datawrapper-vis-Rj6rl"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/Rj6rl/full.png?unq=keystone-sda" alt="Initiative sur l'alimentation: résultats cantonaux (Tableau)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>Iniziativa sull'alimentazione</t>
+  </si>
+  <si>
+    <t>6LUY8</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/6LUY8/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="Iniziativa sull'alimentazione" aria-label="Mappa coropletica" id="datawrapper-chart-6LUY8" src="https://datawrapper.dwcdn.net/6LUY8/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="515" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:515px" id="datawrapper-vis-6LUY8"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/6LUY8/embed.js" charset="utf-8" data-target="#datawrapper-vis-6LUY8"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/6LUY8/full.png?unq=keystone-sda" alt="Iniziativa sull'alimentazione (Mappa coropletica)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>47KQL</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/47KQL/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="Iniziativa sull'alimentazione" aria-label="Mappa coropletica" id="datawrapper-chart-47KQL" src="https://datawrapper.dwcdn.net/47KQL/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="515" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:515px" id="datawrapper-vis-47KQL"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/47KQL/embed.js" charset="utf-8" data-target="#datawrapper-vis-47KQL"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/47KQL/full.png?unq=keystone-sda" alt="Iniziativa sull'alimentazione (Mappa coropletica)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>Iniziativa sull'alimentazione: panoramica dei cantoni</t>
+  </si>
+  <si>
+    <t>abrf7</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/abrf7/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="Iniziativa sull'alimentazione: panoramica dei cantoni" aria-label="Tabella" id="datawrapper-chart-abrf7" src="https://datawrapper.dwcdn.net/abrf7/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="1402" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:1402px" id="datawrapper-vis-abrf7"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/abrf7/embed.js" charset="utf-8" data-target="#datawrapper-vis-abrf7"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/abrf7/full.png?unq=keystone-sda" alt="Iniziativa sull'alimentazione: panoramica dei cantoni (Tabella)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>AG: Neutralitätsinitiative</t>
+  </si>
+  <si>
+    <t>lcQ5X</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/lcQ5X/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="AG: Neutralitätsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-lcQ5X" src="https://datawrapper.dwcdn.net/lcQ5X/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-lcQ5X"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/lcQ5X/embed.js" charset="utf-8" data-target="#datawrapper-vis-lcQ5X"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/lcQ5X/full.png?unq=keystone-sda" alt="AG: Neutralitätsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>AG: Ernährungsinitiative</t>
+  </si>
+  <si>
+    <t>oMz1E</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/oMz1E/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="AG: Ernährungsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-oMz1E" src="https://datawrapper.dwcdn.net/oMz1E/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-oMz1E"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/oMz1E/embed.js" charset="utf-8" data-target="#datawrapper-vis-oMz1E"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/oMz1E/full.png?unq=keystone-sda" alt="AG: Ernährungsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>AI: Neutralitätsinitiative</t>
+  </si>
+  <si>
+    <t>RF2go</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/RF2go/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="AI: Neutralitätsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-RF2go" src="https://datawrapper.dwcdn.net/RF2go/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-RF2go"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/RF2go/embed.js" charset="utf-8" data-target="#datawrapper-vis-RF2go"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/RF2go/full.png?unq=keystone-sda" alt="AI: Neutralitätsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>AI: Ernährungsinitiative</t>
+  </si>
+  <si>
+    <t>qIpUi</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/qIpUi/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="AI: Ernährungsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-qIpUi" src="https://datawrapper.dwcdn.net/qIpUi/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-qIpUi"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/qIpUi/embed.js" charset="utf-8" data-target="#datawrapper-vis-qIpUi"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/qIpUi/full.png?unq=keystone-sda" alt="AI: Ernährungsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>AR: Neutralitätsinitiative</t>
+  </si>
+  <si>
+    <t>N2rJw</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/N2rJw/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="AR: Neutralitätsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-N2rJw" src="https://datawrapper.dwcdn.net/N2rJw/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-N2rJw"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/N2rJw/embed.js" charset="utf-8" data-target="#datawrapper-vis-N2rJw"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/N2rJw/full.png?unq=keystone-sda" alt="AR: Neutralitätsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>AR: Ernährungsinitiative</t>
+  </si>
+  <si>
+    <t>T4y19</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/T4y19/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="AR: Ernährungsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-T4y19" src="https://datawrapper.dwcdn.net/T4y19/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-T4y19"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/T4y19/embed.js" charset="utf-8" data-target="#datawrapper-vis-T4y19"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/T4y19/full.png?unq=keystone-sda" alt="AR: Ernährungsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>BE: Neutralitätsinitiative</t>
+  </si>
+  <si>
+    <t>a36za</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/a36za/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="BE: Neutralitätsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-a36za" src="https://datawrapper.dwcdn.net/a36za/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-a36za"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/a36za/embed.js" charset="utf-8" data-target="#datawrapper-vis-a36za"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/a36za/full.png?unq=keystone-sda" alt="BE: Neutralitätsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>BE: Initiative sur la neutralité</t>
+  </si>
+  <si>
+    <t>L0xtV</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/L0xtV/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="BE: Initiative sur la neutralité" aria-label="Carte choroplèthe" id="datawrapper-chart-L0xtV" src="https://datawrapper.dwcdn.net/L0xtV/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-L0xtV"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/L0xtV/embed.js" charset="utf-8" data-target="#datawrapper-vis-L0xtV"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/L0xtV/full.png?unq=keystone-sda" alt="BE: Initiative sur la neutralité (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>BE: Ernährungsinitiative</t>
+  </si>
+  <si>
+    <t>4QKtU</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/4QKtU/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="BE: Ernährungsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-4QKtU" src="https://datawrapper.dwcdn.net/4QKtU/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-4QKtU"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/4QKtU/embed.js" charset="utf-8" data-target="#datawrapper-vis-4QKtU"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/4QKtU/full.png?unq=keystone-sda" alt="BE: Ernährungsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>BE: Initiative sur l'alimentation</t>
+  </si>
+  <si>
+    <t>a1YBp</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/a1YBp/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="BE: Initiative sur l'alimentation" aria-label="Carte choroplèthe" id="datawrapper-chart-a1YBp" src="https://datawrapper.dwcdn.net/a1YBp/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-a1YBp"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/a1YBp/embed.js" charset="utf-8" data-target="#datawrapper-vis-a1YBp"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/a1YBp/full.png?unq=keystone-sda" alt="BE: Initiative sur l'alimentation (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>BL: Neutralitätsinitiative</t>
+  </si>
+  <si>
+    <t>XApyC</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/XApyC/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="BL: Neutralitätsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-XApyC" src="https://datawrapper.dwcdn.net/XApyC/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-XApyC"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/XApyC/embed.js" charset="utf-8" data-target="#datawrapper-vis-XApyC"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/XApyC/full.png?unq=keystone-sda" alt="BL: Neutralitätsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>BL: Ernährungsinitiative</t>
+  </si>
+  <si>
+    <t>aEKdt</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/aEKdt/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="BL: Ernährungsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-aEKdt" src="https://datawrapper.dwcdn.net/aEKdt/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-aEKdt"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/aEKdt/embed.js" charset="utf-8" data-target="#datawrapper-vis-aEKdt"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/aEKdt/full.png?unq=keystone-sda" alt="BL: Ernährungsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>BS: Neutralitätsinitiative</t>
+  </si>
+  <si>
+    <t>Qlcgb</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/Qlcgb/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="BS: Neutralitätsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-Qlcgb" src="https://datawrapper.dwcdn.net/Qlcgb/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-Qlcgb"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/Qlcgb/embed.js" charset="utf-8" data-target="#datawrapper-vis-Qlcgb"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/Qlcgb/full.png?unq=keystone-sda" alt="BS: Neutralitätsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>BS: Ernährungsinitiative</t>
+  </si>
+  <si>
+    <t>rxAh5</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/rxAh5/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="BS: Ernährungsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-rxAh5" src="https://datawrapper.dwcdn.net/rxAh5/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-rxAh5"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/rxAh5/embed.js" charset="utf-8" data-target="#datawrapper-vis-rxAh5"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/rxAh5/full.png?unq=keystone-sda" alt="BS: Ernährungsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>FR: Neutralitätsinitiative</t>
+  </si>
+  <si>
+    <t>96RU3</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/96RU3/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="FR: Neutralitätsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-96RU3" src="https://datawrapper.dwcdn.net/96RU3/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-96RU3"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/96RU3/embed.js" charset="utf-8" data-target="#datawrapper-vis-96RU3"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/96RU3/full.png?unq=keystone-sda" alt="FR: Neutralitätsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>FR: Initiative sur la neutralité</t>
+  </si>
+  <si>
+    <t>njDjL</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/njDjL/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="FR: Initiative sur la neutralité" aria-label="Carte choroplèthe" id="datawrapper-chart-njDjL" src="https://datawrapper.dwcdn.net/njDjL/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-njDjL"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/njDjL/embed.js" charset="utf-8" data-target="#datawrapper-vis-njDjL"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/njDjL/full.png?unq=keystone-sda" alt="FR: Initiative sur la neutralité (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>FR: Ernährungsinitiative</t>
+  </si>
+  <si>
+    <t>kAcmz</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/kAcmz/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="FR: Ernährungsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-kAcmz" src="https://datawrapper.dwcdn.net/kAcmz/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-kAcmz"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/kAcmz/embed.js" charset="utf-8" data-target="#datawrapper-vis-kAcmz"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/kAcmz/full.png?unq=keystone-sda" alt="FR: Ernährungsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>FR: Initiative sur l'alimentation</t>
+  </si>
+  <si>
+    <t>t4QDT</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/t4QDT/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="FR: Initiative sur l'alimentation" aria-label="Carte choroplèthe" id="datawrapper-chart-t4QDT" src="https://datawrapper.dwcdn.net/t4QDT/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-t4QDT"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/t4QDT/embed.js" charset="utf-8" data-target="#datawrapper-vis-t4QDT"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/t4QDT/full.png?unq=keystone-sda" alt="FR: Initiative sur l'alimentation (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>GE: Initiative sur la neutralité</t>
+  </si>
+  <si>
+    <t>U3NCl</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/U3NCl/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="GE: Initiative sur la neutralité" aria-label="Carte choroplèthe" id="datawrapper-chart-U3NCl" src="https://datawrapper.dwcdn.net/U3NCl/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-U3NCl"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/U3NCl/embed.js" charset="utf-8" data-target="#datawrapper-vis-U3NCl"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/U3NCl/full.png?unq=keystone-sda" alt="GE: Initiative sur la neutralité (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>GE: Initiative sur l'alimentation</t>
+  </si>
+  <si>
+    <t>e6ILY</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/e6ILY/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="GE: Initiative sur l'alimentation" aria-label="Carte choroplèthe" id="datawrapper-chart-e6ILY" src="https://datawrapper.dwcdn.net/e6ILY/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-e6ILY"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/e6ILY/embed.js" charset="utf-8" data-target="#datawrapper-vis-e6ILY"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/e6ILY/full.png?unq=keystone-sda" alt="GE: Initiative sur l'alimentation (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>GL: Neutralitätsinitiative</t>
+  </si>
+  <si>
+    <t>9gMl7</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/9gMl7/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="GL: Neutralitätsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-9gMl7" src="https://datawrapper.dwcdn.net/9gMl7/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-9gMl7"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/9gMl7/embed.js" charset="utf-8" data-target="#datawrapper-vis-9gMl7"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/9gMl7/full.png?unq=keystone-sda" alt="GL: Neutralitätsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>GL: Ernährungsinitiative</t>
+  </si>
+  <si>
+    <t>2Rjul</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/2Rjul/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="GL: Ernährungsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-2Rjul" src="https://datawrapper.dwcdn.net/2Rjul/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-2Rjul"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/2Rjul/embed.js" charset="utf-8" data-target="#datawrapper-vis-2Rjul"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/2Rjul/full.png?unq=keystone-sda" alt="GL: Ernährungsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>GR: Neutralitätsinitiative</t>
+  </si>
+  <si>
+    <t>ealOD</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/ealOD/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="GR: Neutralitätsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-ealOD" src="https://datawrapper.dwcdn.net/ealOD/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-ealOD"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/ealOD/embed.js" charset="utf-8" data-target="#datawrapper-vis-ealOD"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/ealOD/full.png?unq=keystone-sda" alt="GR: Neutralitätsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>GR: Iniziativa sulla neutralità</t>
+  </si>
+  <si>
+    <t>k8tlf</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/k8tlf/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="GR: Iniziativa sulla neutralità" aria-label="Mappa coropletica" id="datawrapper-chart-k8tlf" src="https://datawrapper.dwcdn.net/k8tlf/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="515" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:515px" id="datawrapper-vis-k8tlf"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/k8tlf/embed.js" charset="utf-8" data-target="#datawrapper-vis-k8tlf"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/k8tlf/full.png?unq=keystone-sda" alt="GR: Iniziativa sulla neutralità (Mappa coropletica)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>GR: Ernährungsinitiative</t>
+  </si>
+  <si>
+    <t>Rak1T</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/Rak1T/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="GR: Ernährungsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-Rak1T" src="https://datawrapper.dwcdn.net/Rak1T/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-Rak1T"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/Rak1T/embed.js" charset="utf-8" data-target="#datawrapper-vis-Rak1T"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/Rak1T/full.png?unq=keystone-sda" alt="GR: Ernährungsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>GR: Iniziativa sull'alimentazione</t>
+  </si>
+  <si>
+    <t>6mkrR</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/6mkrR/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="GR: Iniziativa sull'alimentazione" aria-label="Mappa coropletica" id="datawrapper-chart-6mkrR" src="https://datawrapper.dwcdn.net/6mkrR/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="515" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:515px" id="datawrapper-vis-6mkrR"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/6mkrR/embed.js" charset="utf-8" data-target="#datawrapper-vis-6mkrR"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/6mkrR/full.png?unq=keystone-sda" alt="GR: Iniziativa sull'alimentazione (Mappa coropletica)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>JU: Initiative sur la neutralité</t>
+  </si>
+  <si>
+    <t>mrjos</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/mrjos/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="JU: Initiative sur la neutralité" aria-label="Carte choroplèthe" id="datawrapper-chart-mrjos" src="https://datawrapper.dwcdn.net/mrjos/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-mrjos"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/mrjos/embed.js" charset="utf-8" data-target="#datawrapper-vis-mrjos"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/mrjos/full.png?unq=keystone-sda" alt="JU: Initiative sur la neutralité (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>JU: Initiative sur l'alimentation</t>
+  </si>
+  <si>
+    <t>bVDsI</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/bVDsI/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="JU: Initiative sur l'alimentation" aria-label="Carte choroplèthe" id="datawrapper-chart-bVDsI" src="https://datawrapper.dwcdn.net/bVDsI/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-bVDsI"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/bVDsI/embed.js" charset="utf-8" data-target="#datawrapper-vis-bVDsI"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/bVDsI/full.png?unq=keystone-sda" alt="JU: Initiative sur l'alimentation (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>LU: Neutralitätsinitiative</t>
+  </si>
+  <si>
+    <t>B7zK2</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/B7zK2/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="LU: Neutralitätsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-B7zK2" src="https://datawrapper.dwcdn.net/B7zK2/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-B7zK2"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/B7zK2/embed.js" charset="utf-8" data-target="#datawrapper-vis-B7zK2"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/B7zK2/full.png?unq=keystone-sda" alt="LU: Neutralitätsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>LU: Ernährungsinitiative</t>
+  </si>
+  <si>
+    <t>HbKeu</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/HbKeu/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="LU: Ernährungsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-HbKeu" src="https://datawrapper.dwcdn.net/HbKeu/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-HbKeu"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/HbKeu/embed.js" charset="utf-8" data-target="#datawrapper-vis-HbKeu"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/HbKeu/full.png?unq=keystone-sda" alt="LU: Ernährungsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>NE: Initiative sur la neutralité</t>
+  </si>
+  <si>
+    <t>8EWT4</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/8EWT4/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="NE: Initiative sur la neutralité" aria-label="Carte choroplèthe" id="datawrapper-chart-8EWT4" src="https://datawrapper.dwcdn.net/8EWT4/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-8EWT4"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/8EWT4/embed.js" charset="utf-8" data-target="#datawrapper-vis-8EWT4"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/8EWT4/full.png?unq=keystone-sda" alt="NE: Initiative sur la neutralité (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>NE: Initiative sur l'alimentation</t>
+  </si>
+  <si>
+    <t>rxnzq</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/rxnzq/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="NE: Initiative sur l'alimentation" aria-label="Carte choroplèthe" id="datawrapper-chart-rxnzq" src="https://datawrapper.dwcdn.net/rxnzq/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-rxnzq"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/rxnzq/embed.js" charset="utf-8" data-target="#datawrapper-vis-rxnzq"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/rxnzq/full.png?unq=keystone-sda" alt="NE: Initiative sur l'alimentation (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>NW: Neutralitätsinitiative</t>
+  </si>
+  <si>
+    <t>AQt7p</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/AQt7p/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="NW: Neutralitätsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-AQt7p" src="https://datawrapper.dwcdn.net/AQt7p/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-AQt7p"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/AQt7p/embed.js" charset="utf-8" data-target="#datawrapper-vis-AQt7p"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/AQt7p/full.png?unq=keystone-sda" alt="NW: Neutralitätsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>NW: Ernährungsinitiative</t>
+  </si>
+  <si>
+    <t>HodeB</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/HodeB/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="NW: Ernährungsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-HodeB" src="https://datawrapper.dwcdn.net/HodeB/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-HodeB"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/HodeB/embed.js" charset="utf-8" data-target="#datawrapper-vis-HodeB"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/HodeB/full.png?unq=keystone-sda" alt="NW: Ernährungsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>OW: Neutralitätsinitiative</t>
+  </si>
+  <si>
+    <t>eLgp5</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/eLgp5/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="OW: Neutralitätsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-eLgp5" src="https://datawrapper.dwcdn.net/eLgp5/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-eLgp5"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/eLgp5/embed.js" charset="utf-8" data-target="#datawrapper-vis-eLgp5"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/eLgp5/full.png?unq=keystone-sda" alt="OW: Neutralitätsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>OW: Ernährungsinitiative</t>
+  </si>
+  <si>
+    <t>lE9ZS</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/lE9ZS/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="OW: Ernährungsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-lE9ZS" src="https://datawrapper.dwcdn.net/lE9ZS/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-lE9ZS"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/lE9ZS/embed.js" charset="utf-8" data-target="#datawrapper-vis-lE9ZS"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/lE9ZS/full.png?unq=keystone-sda" alt="OW: Ernährungsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>SG: Neutralitätsinitiative</t>
+  </si>
+  <si>
+    <t>COVwt</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/COVwt/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="SG: Neutralitätsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-COVwt" src="https://datawrapper.dwcdn.net/COVwt/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-COVwt"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/COVwt/embed.js" charset="utf-8" data-target="#datawrapper-vis-COVwt"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/COVwt/full.png?unq=keystone-sda" alt="SG: Neutralitätsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>SG: Ernährungsinitiative</t>
+  </si>
+  <si>
+    <t>FL9kK</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/FL9kK/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="SG: Ernährungsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-FL9kK" src="https://datawrapper.dwcdn.net/FL9kK/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-FL9kK"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/FL9kK/embed.js" charset="utf-8" data-target="#datawrapper-vis-FL9kK"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/FL9kK/full.png?unq=keystone-sda" alt="SG: Ernährungsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>SH: Neutralitätsinitiative</t>
+  </si>
+  <si>
+    <t>batMq</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/batMq/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="SH: Neutralitätsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-batMq" src="https://datawrapper.dwcdn.net/batMq/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-batMq"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/batMq/embed.js" charset="utf-8" data-target="#datawrapper-vis-batMq"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/batMq/full.png?unq=keystone-sda" alt="SH: Neutralitätsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>SH: Ernährungsinitiative</t>
+  </si>
+  <si>
+    <t>URkOj</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/URkOj/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="SH: Ernährungsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-URkOj" src="https://datawrapper.dwcdn.net/URkOj/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-URkOj"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/URkOj/embed.js" charset="utf-8" data-target="#datawrapper-vis-URkOj"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/URkOj/full.png?unq=keystone-sda" alt="SH: Ernährungsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>SO: Neutralitätsinitiative</t>
+  </si>
+  <si>
+    <t>ut30A</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/ut30A/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="SO: Neutralitätsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-ut30A" src="https://datawrapper.dwcdn.net/ut30A/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-ut30A"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/ut30A/embed.js" charset="utf-8" data-target="#datawrapper-vis-ut30A"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/ut30A/full.png?unq=keystone-sda" alt="SO: Neutralitätsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>SO: Ernährungsinitiative</t>
+  </si>
+  <si>
+    <t>srav0</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/srav0/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="SO: Ernährungsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-srav0" src="https://datawrapper.dwcdn.net/srav0/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-srav0"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/srav0/embed.js" charset="utf-8" data-target="#datawrapper-vis-srav0"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/srav0/full.png?unq=keystone-sda" alt="SO: Ernährungsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>SZ: Neutralitätsinitiative</t>
+  </si>
+  <si>
+    <t>h0vtW</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/h0vtW/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="SZ: Neutralitätsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-h0vtW" src="https://datawrapper.dwcdn.net/h0vtW/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-h0vtW"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/h0vtW/embed.js" charset="utf-8" data-target="#datawrapper-vis-h0vtW"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/h0vtW/full.png?unq=keystone-sda" alt="SZ: Neutralitätsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>SZ: Ernährungsinitiative</t>
+  </si>
+  <si>
+    <t>VpKRM</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/VpKRM/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="SZ: Ernährungsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-VpKRM" src="https://datawrapper.dwcdn.net/VpKRM/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-VpKRM"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/VpKRM/embed.js" charset="utf-8" data-target="#datawrapper-vis-VpKRM"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/VpKRM/full.png?unq=keystone-sda" alt="SZ: Ernährungsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>TG: Neutralitätsinitiative</t>
+  </si>
+  <si>
+    <t>AQSOB</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/AQSOB/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="TG: Neutralitätsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-AQSOB" src="https://datawrapper.dwcdn.net/AQSOB/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-AQSOB"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/AQSOB/embed.js" charset="utf-8" data-target="#datawrapper-vis-AQSOB"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/AQSOB/full.png?unq=keystone-sda" alt="TG: Neutralitätsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>TG: Ernährungsinitiative</t>
+  </si>
+  <si>
+    <t>yzUkO</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/yzUkO/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="TG: Ernährungsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-yzUkO" src="https://datawrapper.dwcdn.net/yzUkO/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-yzUkO"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/yzUkO/embed.js" charset="utf-8" data-target="#datawrapper-vis-yzUkO"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/yzUkO/full.png?unq=keystone-sda" alt="TG: Ernährungsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>TI: Iniziativa sulla neutralità</t>
+  </si>
+  <si>
+    <t>EvKnB</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/EvKnB/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="TI: Iniziativa sulla neutralità" aria-label="Mappa coropletica" id="datawrapper-chart-EvKnB" src="https://datawrapper.dwcdn.net/EvKnB/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="515" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:515px" id="datawrapper-vis-EvKnB"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/EvKnB/embed.js" charset="utf-8" data-target="#datawrapper-vis-EvKnB"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/EvKnB/full.png?unq=keystone-sda" alt="TI: Iniziativa sulla neutralità (Mappa coropletica)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>TI: Iniziativa sull'alimentazione</t>
+  </si>
+  <si>
+    <t>K7T65</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/K7T65/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="TI: Iniziativa sull'alimentazione" aria-label="Mappa coropletica" id="datawrapper-chart-K7T65" src="https://datawrapper.dwcdn.net/K7T65/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="515" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:515px" id="datawrapper-vis-K7T65"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/K7T65/embed.js" charset="utf-8" data-target="#datawrapper-vis-K7T65"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/K7T65/full.png?unq=keystone-sda" alt="TI: Iniziativa sull'alimentazione (Mappa coropletica)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>UR: Neutralitätsinitiative</t>
+  </si>
+  <si>
+    <t>ARRfh</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/ARRfh/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="UR: Neutralitätsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-ARRfh" src="https://datawrapper.dwcdn.net/ARRfh/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-ARRfh"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/ARRfh/embed.js" charset="utf-8" data-target="#datawrapper-vis-ARRfh"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/ARRfh/full.png?unq=keystone-sda" alt="UR: Neutralitätsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>UR: Ernährungsinitiative</t>
+  </si>
+  <si>
+    <t>y2cko</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/y2cko/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="UR: Ernährungsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-y2cko" src="https://datawrapper.dwcdn.net/y2cko/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-y2cko"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/y2cko/embed.js" charset="utf-8" data-target="#datawrapper-vis-y2cko"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/y2cko/full.png?unq=keystone-sda" alt="UR: Ernährungsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>VD: Initiative sur la neutralité</t>
+  </si>
+  <si>
+    <t>qcug1</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/qcug1/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="VD: Initiative sur la neutralité" aria-label="Carte choroplèthe" id="datawrapper-chart-qcug1" src="https://datawrapper.dwcdn.net/qcug1/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-qcug1"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/qcug1/embed.js" charset="utf-8" data-target="#datawrapper-vis-qcug1"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/qcug1/full.png?unq=keystone-sda" alt="VD: Initiative sur la neutralité (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>VD: Initiative sur l'alimentation</t>
+  </si>
+  <si>
+    <t>XXLoR</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/XXLoR/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="VD: Initiative sur l'alimentation" aria-label="Carte choroplèthe" id="datawrapper-chart-XXLoR" src="https://datawrapper.dwcdn.net/XXLoR/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-XXLoR"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/XXLoR/embed.js" charset="utf-8" data-target="#datawrapper-vis-XXLoR"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/XXLoR/full.png?unq=keystone-sda" alt="VD: Initiative sur l'alimentation (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>VS: Neutralitätsinitiative</t>
+  </si>
+  <si>
+    <t>sHYvS</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/sHYvS/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="VS: Neutralitätsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-sHYvS" src="https://datawrapper.dwcdn.net/sHYvS/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-sHYvS"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/sHYvS/embed.js" charset="utf-8" data-target="#datawrapper-vis-sHYvS"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/sHYvS/full.png?unq=keystone-sda" alt="VS: Neutralitätsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>VS: Initiative sur la neutralité</t>
+  </si>
+  <si>
+    <t>zOWFJ</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/zOWFJ/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="VS: Initiative sur la neutralité" aria-label="Carte choroplèthe" id="datawrapper-chart-zOWFJ" src="https://datawrapper.dwcdn.net/zOWFJ/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-zOWFJ"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/zOWFJ/embed.js" charset="utf-8" data-target="#datawrapper-vis-zOWFJ"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/zOWFJ/full.png?unq=keystone-sda" alt="VS: Initiative sur la neutralité (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>VS: Ernährungsinitiative</t>
+  </si>
+  <si>
+    <t>P11F9</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/P11F9/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="VS: Ernährungsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-P11F9" src="https://datawrapper.dwcdn.net/P11F9/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-P11F9"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/P11F9/embed.js" charset="utf-8" data-target="#datawrapper-vis-P11F9"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/P11F9/full.png?unq=keystone-sda" alt="VS: Ernährungsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>VS: Initiative sur l'alimentation</t>
+  </si>
+  <si>
+    <t>STVf0</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/STVf0/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="VS: Initiative sur l'alimentation" aria-label="Carte choroplèthe" id="datawrapper-chart-STVf0" src="https://datawrapper.dwcdn.net/STVf0/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-STVf0"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/STVf0/embed.js" charset="utf-8" data-target="#datawrapper-vis-STVf0"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/STVf0/full.png?unq=keystone-sda" alt="VS: Initiative sur l'alimentation (Carte choroplèthe)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>ZG: Neutralitätsinitiative</t>
+  </si>
+  <si>
+    <t>MfXcx</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/MfXcx/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="ZG: Neutralitätsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-MfXcx" src="https://datawrapper.dwcdn.net/MfXcx/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-MfXcx"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/MfXcx/embed.js" charset="utf-8" data-target="#datawrapper-vis-MfXcx"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/MfXcx/full.png?unq=keystone-sda" alt="ZG: Neutralitätsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>ZG: Ernährungsinitiative</t>
+  </si>
+  <si>
+    <t>7ToW5</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/7ToW5/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="ZG: Ernährungsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-7ToW5" src="https://datawrapper.dwcdn.net/7ToW5/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-7ToW5"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/7ToW5/embed.js" charset="utf-8" data-target="#datawrapper-vis-7ToW5"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/7ToW5/full.png?unq=keystone-sda" alt="ZG: Ernährungsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>ZH: Neutralitätsinitiative</t>
+  </si>
+  <si>
+    <t>oPH43</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/oPH43/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="ZH: Neutralitätsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-oPH43" src="https://datawrapper.dwcdn.net/oPH43/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-oPH43"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/oPH43/embed.js" charset="utf-8" data-target="#datawrapper-vis-oPH43"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/oPH43/full.png?unq=keystone-sda" alt="ZH: Neutralitätsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
+  </si>
+  <si>
+    <t>ZH: Ernährungsinitiative</t>
+  </si>
+  <si>
+    <t>POlsT</t>
+  </si>
+  <si>
+    <t>https://datawrapper.dwcdn.net/POlsT/1/</t>
+  </si>
+  <si>
+    <t>&lt;iframe title="ZH: Ernährungsinitiative" aria-label="Choroplethen-Karte" id="datawrapper-chart-POlsT" src="https://datawrapper.dwcdn.net/POlsT/1/?unq=keystone-sda" scrolling="no" frameborder="0" style="width: 0; min-width: 100% !important; border: none;" height="495" data-external="1"&gt;&lt;/iframe&gt;&lt;script type="text/javascript"&gt;(function(){function e(){window.addEventListener(`message`,function(e){if(e.data[`datawrapper-height`]!==void 0){var t=document.querySelectorAll(`iframe`);for(var n in e.data[`datawrapper-height`])for(var r=0,i;i=t[r];r++)if(i.contentWindow===e.source){var a=e.data[`datawrapper-height`][n]+`px`;i.style.height=a}}})}e()})();&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div style="min-height:495px" id="datawrapper-vis-POlsT"&gt;&lt;script type="text/javascript" defer src="https://datawrapper.dwcdn.net/POlsT/embed.js" charset="utf-8" data-target="#datawrapper-vis-POlsT"&gt;&lt;/script&gt;&lt;noscript&gt;&lt;img src="https://datawrapper.dwcdn.net/POlsT/full.png?unq=keystone-sda" alt="ZH: Ernährungsinitiative (Choroplethen-Karte)" /&gt;&lt;/noscript&gt;&lt;/div&gt;</t>
   </si>
 </sst>
 </file>
@@ -1874,22 +1874,22 @@
         <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>408</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
       </c>
       <c r="E5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" t="s">
         <v>63</v>
-      </c>
-      <c r="F5" t="s">
-        <v>64</v>
-      </c>
-      <c r="G5" t="s">
-        <v>65</v>
-      </c>
-      <c r="H5" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -1900,22 +1900,22 @@
         <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>408</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
       </c>
       <c r="E6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" t="s">
         <v>67</v>
-      </c>
-      <c r="F6" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" t="s">
-        <v>69</v>
-      </c>
-      <c r="H6" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -1926,22 +1926,22 @@
         <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>409</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
         <v>16</v>
       </c>
       <c r="E7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" t="s">
         <v>71</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
         <v>72</v>
-      </c>
-      <c r="G7" t="s">
-        <v>73</v>
-      </c>
-      <c r="H7" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -1952,22 +1952,22 @@
         <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>431</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
       </c>
       <c r="E8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F8" t="s">
         <v>75</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>76</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>77</v>
-      </c>
-      <c r="H8" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -1978,22 +1978,22 @@
         <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>431</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
       </c>
       <c r="E9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" t="s">
         <v>79</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>80</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>81</v>
-      </c>
-      <c r="H9" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -2004,7 +2004,7 @@
         <v>58</v>
       </c>
       <c r="C10" t="s">
-        <v>432</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
@@ -2030,22 +2030,22 @@
         <v>58</v>
       </c>
       <c r="C11" t="s">
-        <v>440</v>
+        <v>87</v>
       </c>
       <c r="D11" t="s">
         <v>15</v>
       </c>
       <c r="E11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -2056,22 +2056,22 @@
         <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>440</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
         <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -2082,22 +2082,22 @@
         <v>58</v>
       </c>
       <c r="C13" t="s">
-        <v>441</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
         <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H13" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -2105,25 +2105,25 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
         <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F14" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -2131,25 +2131,25 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
         <v>13</v>
       </c>
       <c r="E15" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F15" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G15" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H15" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -2157,25 +2157,25 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="D16" t="s">
         <v>16</v>
       </c>
       <c r="E16" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F16" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G16" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="H16" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -2183,25 +2183,25 @@
         <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="D17" t="s">
         <v>14</v>
       </c>
       <c r="E17" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="F17" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="G17" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="H17" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -2209,25 +2209,25 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="D18" t="s">
         <v>14</v>
       </c>
       <c r="E18" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F18" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="G18" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="H18" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -2235,25 +2235,25 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C19" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D19" t="s">
         <v>14</v>
       </c>
       <c r="E19" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F19" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G19" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="H19" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -2261,25 +2261,25 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C20" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D20" t="s">
         <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="F20" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="G20" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="H20" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -2287,25 +2287,25 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C21" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D21" t="s">
         <v>15</v>
       </c>
       <c r="E21" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="F21" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="G21" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="H21" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -2313,25 +2313,25 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C22" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D22" t="s">
         <v>15</v>
       </c>
       <c r="E22" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="F22" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="G22" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="H22" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -2386,22 +2386,22 @@
         <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>410</v>
+        <v>144</v>
       </c>
       <c r="D2" t="s">
         <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="G2" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="H2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2409,25 +2409,25 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="F3" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="G3" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="H3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2438,22 +2438,22 @@
         <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>411</v>
+        <v>154</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="F4" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="G4" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="H4" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -2461,25 +2461,25 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F5" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="G5" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="H5" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -2490,22 +2490,22 @@
         <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>412</v>
+        <v>164</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="F6" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="G6" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="H6" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -2513,25 +2513,25 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C7" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="F7" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="G7" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="H7" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -2542,22 +2542,22 @@
         <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>413</v>
+        <v>174</v>
       </c>
       <c r="D8" t="s">
         <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="F8" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="G8" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="H8" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -2568,22 +2568,22 @@
         <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>433</v>
+        <v>179</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="F9" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="G9" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="H9" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -2591,25 +2591,25 @@
         <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C10" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D10" t="s">
         <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="F10" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="G10" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="H10" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -2617,25 +2617,25 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C11" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
       </c>
       <c r="E11" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="F11" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="G11" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="H11" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -2646,22 +2646,22 @@
         <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>414</v>
+        <v>194</v>
       </c>
       <c r="D12" t="s">
         <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="F12" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="G12" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="H12" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -2669,25 +2669,25 @@
         <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C13" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="D13" t="s">
         <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="F13" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="G13" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="H13" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -2698,22 +2698,22 @@
         <v>58</v>
       </c>
       <c r="C14" t="s">
-        <v>415</v>
+        <v>204</v>
       </c>
       <c r="D14" t="s">
         <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="F14" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="G14" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="H14" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -2721,25 +2721,25 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C15" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="D15" t="s">
         <v>13</v>
       </c>
       <c r="E15" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="F15" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="G15" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="H15" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -2750,22 +2750,22 @@
         <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>416</v>
+        <v>214</v>
       </c>
       <c r="D16" t="s">
         <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="F16" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="G16" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="H16" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -2776,22 +2776,22 @@
         <v>58</v>
       </c>
       <c r="C17" t="s">
-        <v>434</v>
+        <v>219</v>
       </c>
       <c r="D17" t="s">
         <v>14</v>
       </c>
       <c r="E17" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="F17" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="G17" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="H17" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -2799,25 +2799,25 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C18" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="D18" t="s">
         <v>13</v>
       </c>
       <c r="E18" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="F18" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="G18" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="H18" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -2825,25 +2825,25 @@
         <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C19" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="D19" t="s">
         <v>14</v>
       </c>
       <c r="E19" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="F19" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="G19" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="H19" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -2854,22 +2854,22 @@
         <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>435</v>
+        <v>234</v>
       </c>
       <c r="D20" t="s">
         <v>14</v>
       </c>
       <c r="E20" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="F20" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="G20" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="H20" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -2877,25 +2877,25 @@
         <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C21" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="D21" t="s">
         <v>14</v>
       </c>
       <c r="E21" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="F21" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="G21" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="H21" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -2906,22 +2906,22 @@
         <v>58</v>
       </c>
       <c r="C22" t="s">
-        <v>417</v>
+        <v>244</v>
       </c>
       <c r="D22" t="s">
         <v>13</v>
       </c>
       <c r="E22" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="F22" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="G22" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="H22" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -2929,25 +2929,25 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C23" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="D23" t="s">
         <v>13</v>
       </c>
       <c r="E23" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="F23" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="G23" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="H23" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -2958,22 +2958,22 @@
         <v>58</v>
       </c>
       <c r="C24" t="s">
-        <v>418</v>
+        <v>254</v>
       </c>
       <c r="D24" t="s">
         <v>13</v>
       </c>
       <c r="E24" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="F24" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="G24" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="H24" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -2984,22 +2984,22 @@
         <v>58</v>
       </c>
       <c r="C25" t="s">
-        <v>442</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
         <v>15</v>
       </c>
       <c r="E25" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="F25" t="s">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="G25" t="s">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="H25" t="s">
-        <v>244</v>
+        <v>263</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -3007,25 +3007,25 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C26" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="D26" t="s">
         <v>13</v>
       </c>
       <c r="E26" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="F26" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="G26" t="s">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="H26" t="s">
-        <v>249</v>
+        <v>268</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -3033,25 +3033,25 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C27" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="D27" t="s">
         <v>15</v>
       </c>
       <c r="E27" t="s">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="F27" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="G27" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="H27" t="s">
-        <v>254</v>
+        <v>273</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -3062,22 +3062,22 @@
         <v>58</v>
       </c>
       <c r="C28" t="s">
-        <v>436</v>
+        <v>274</v>
       </c>
       <c r="D28" t="s">
         <v>14</v>
       </c>
       <c r="E28" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="F28" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="G28" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="H28" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -3085,25 +3085,25 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="D29" t="s">
         <v>14</v>
       </c>
       <c r="E29" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="F29" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="G29" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="H29" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -3114,22 +3114,22 @@
         <v>58</v>
       </c>
       <c r="C30" t="s">
-        <v>419</v>
+        <v>284</v>
       </c>
       <c r="D30" t="s">
         <v>13</v>
       </c>
       <c r="E30" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="F30" t="s">
-        <v>265</v>
+        <v>286</v>
       </c>
       <c r="G30" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="H30" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -3137,25 +3137,25 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C31" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="D31" t="s">
         <v>13</v>
       </c>
       <c r="E31" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="F31" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="G31" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H31" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -3166,22 +3166,22 @@
         <v>58</v>
       </c>
       <c r="C32" t="s">
-        <v>437</v>
+        <v>294</v>
       </c>
       <c r="D32" t="s">
         <v>14</v>
       </c>
       <c r="E32" t="s">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="F32" t="s">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="G32" t="s">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="H32" t="s">
-        <v>276</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -3189,25 +3189,25 @@
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C33" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="D33" t="s">
         <v>14</v>
       </c>
       <c r="E33" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="F33" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="G33" t="s">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="H33" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -3218,22 +3218,22 @@
         <v>58</v>
       </c>
       <c r="C34" t="s">
-        <v>420</v>
+        <v>304</v>
       </c>
       <c r="D34" t="s">
         <v>13</v>
       </c>
       <c r="E34" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="F34" t="s">
-        <v>283</v>
+        <v>306</v>
       </c>
       <c r="G34" t="s">
-        <v>284</v>
+        <v>307</v>
       </c>
       <c r="H34" t="s">
-        <v>285</v>
+        <v>308</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -3241,25 +3241,25 @@
         <v>30</v>
       </c>
       <c r="B35" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C35" t="s">
-        <v>286</v>
+        <v>309</v>
       </c>
       <c r="D35" t="s">
         <v>13</v>
       </c>
       <c r="E35" t="s">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="F35" t="s">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="G35" t="s">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="H35" t="s">
-        <v>290</v>
+        <v>313</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -3270,22 +3270,22 @@
         <v>58</v>
       </c>
       <c r="C36" t="s">
-        <v>421</v>
+        <v>314</v>
       </c>
       <c r="D36" t="s">
         <v>13</v>
       </c>
       <c r="E36" t="s">
-        <v>291</v>
+        <v>315</v>
       </c>
       <c r="F36" t="s">
-        <v>292</v>
+        <v>316</v>
       </c>
       <c r="G36" t="s">
-        <v>293</v>
+        <v>317</v>
       </c>
       <c r="H36" t="s">
-        <v>294</v>
+        <v>318</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -3293,25 +3293,25 @@
         <v>31</v>
       </c>
       <c r="B37" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C37" t="s">
-        <v>295</v>
+        <v>319</v>
       </c>
       <c r="D37" t="s">
         <v>13</v>
       </c>
       <c r="E37" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="F37" t="s">
-        <v>297</v>
+        <v>321</v>
       </c>
       <c r="G37" t="s">
-        <v>298</v>
+        <v>322</v>
       </c>
       <c r="H37" t="s">
-        <v>299</v>
+        <v>323</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -3322,22 +3322,22 @@
         <v>58</v>
       </c>
       <c r="C38" t="s">
-        <v>422</v>
+        <v>324</v>
       </c>
       <c r="D38" t="s">
         <v>13</v>
       </c>
       <c r="E38" t="s">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="F38" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="G38" t="s">
-        <v>302</v>
+        <v>327</v>
       </c>
       <c r="H38" t="s">
-        <v>303</v>
+        <v>328</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -3345,25 +3345,25 @@
         <v>32</v>
       </c>
       <c r="B39" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C39" t="s">
-        <v>304</v>
+        <v>329</v>
       </c>
       <c r="D39" t="s">
         <v>13</v>
       </c>
       <c r="E39" t="s">
-        <v>305</v>
+        <v>330</v>
       </c>
       <c r="F39" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="G39" t="s">
-        <v>307</v>
+        <v>332</v>
       </c>
       <c r="H39" t="s">
-        <v>308</v>
+        <v>333</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -3374,22 +3374,22 @@
         <v>58</v>
       </c>
       <c r="C40" t="s">
-        <v>423</v>
+        <v>334</v>
       </c>
       <c r="D40" t="s">
         <v>13</v>
       </c>
       <c r="E40" t="s">
-        <v>309</v>
+        <v>335</v>
       </c>
       <c r="F40" t="s">
-        <v>310</v>
+        <v>336</v>
       </c>
       <c r="G40" t="s">
-        <v>311</v>
+        <v>337</v>
       </c>
       <c r="H40" t="s">
-        <v>312</v>
+        <v>338</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -3397,25 +3397,25 @@
         <v>33</v>
       </c>
       <c r="B41" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C41" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="D41" t="s">
         <v>13</v>
       </c>
       <c r="E41" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="F41" t="s">
-        <v>315</v>
+        <v>341</v>
       </c>
       <c r="G41" t="s">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="H41" t="s">
-        <v>317</v>
+        <v>343</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -3426,22 +3426,22 @@
         <v>58</v>
       </c>
       <c r="C42" t="s">
-        <v>424</v>
+        <v>344</v>
       </c>
       <c r="D42" t="s">
         <v>13</v>
       </c>
       <c r="E42" t="s">
-        <v>318</v>
+        <v>345</v>
       </c>
       <c r="F42" t="s">
-        <v>319</v>
+        <v>346</v>
       </c>
       <c r="G42" t="s">
-        <v>320</v>
+        <v>347</v>
       </c>
       <c r="H42" t="s">
-        <v>321</v>
+        <v>348</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -3449,25 +3449,25 @@
         <v>34</v>
       </c>
       <c r="B43" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C43" t="s">
-        <v>322</v>
+        <v>349</v>
       </c>
       <c r="D43" t="s">
         <v>13</v>
       </c>
       <c r="E43" t="s">
-        <v>323</v>
+        <v>350</v>
       </c>
       <c r="F43" t="s">
-        <v>324</v>
+        <v>351</v>
       </c>
       <c r="G43" t="s">
-        <v>325</v>
+        <v>352</v>
       </c>
       <c r="H43" t="s">
-        <v>326</v>
+        <v>353</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -3478,22 +3478,22 @@
         <v>58</v>
       </c>
       <c r="C44" t="s">
-        <v>425</v>
+        <v>354</v>
       </c>
       <c r="D44" t="s">
         <v>13</v>
       </c>
       <c r="E44" t="s">
-        <v>327</v>
+        <v>355</v>
       </c>
       <c r="F44" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="G44" t="s">
-        <v>329</v>
+        <v>357</v>
       </c>
       <c r="H44" t="s">
-        <v>330</v>
+        <v>358</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -3501,25 +3501,25 @@
         <v>35</v>
       </c>
       <c r="B45" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C45" t="s">
-        <v>331</v>
+        <v>359</v>
       </c>
       <c r="D45" t="s">
         <v>13</v>
       </c>
       <c r="E45" t="s">
-        <v>332</v>
+        <v>360</v>
       </c>
       <c r="F45" t="s">
-        <v>333</v>
+        <v>361</v>
       </c>
       <c r="G45" t="s">
-        <v>334</v>
+        <v>362</v>
       </c>
       <c r="H45" t="s">
-        <v>335</v>
+        <v>363</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -3530,22 +3530,22 @@
         <v>58</v>
       </c>
       <c r="C46" t="s">
-        <v>426</v>
+        <v>364</v>
       </c>
       <c r="D46" t="s">
         <v>13</v>
       </c>
       <c r="E46" t="s">
-        <v>336</v>
+        <v>365</v>
       </c>
       <c r="F46" t="s">
-        <v>337</v>
+        <v>366</v>
       </c>
       <c r="G46" t="s">
-        <v>338</v>
+        <v>367</v>
       </c>
       <c r="H46" t="s">
-        <v>339</v>
+        <v>368</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -3553,25 +3553,25 @@
         <v>36</v>
       </c>
       <c r="B47" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C47" t="s">
-        <v>340</v>
+        <v>369</v>
       </c>
       <c r="D47" t="s">
         <v>13</v>
       </c>
       <c r="E47" t="s">
-        <v>341</v>
+        <v>370</v>
       </c>
       <c r="F47" t="s">
-        <v>342</v>
+        <v>371</v>
       </c>
       <c r="G47" t="s">
-        <v>343</v>
+        <v>372</v>
       </c>
       <c r="H47" t="s">
-        <v>344</v>
+        <v>373</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -3582,22 +3582,22 @@
         <v>58</v>
       </c>
       <c r="C48" t="s">
-        <v>443</v>
+        <v>374</v>
       </c>
       <c r="D48" t="s">
         <v>15</v>
       </c>
       <c r="E48" t="s">
-        <v>345</v>
+        <v>375</v>
       </c>
       <c r="F48" t="s">
-        <v>346</v>
+        <v>376</v>
       </c>
       <c r="G48" t="s">
-        <v>347</v>
+        <v>377</v>
       </c>
       <c r="H48" t="s">
-        <v>348</v>
+        <v>378</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -3605,25 +3605,25 @@
         <v>37</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C49" t="s">
-        <v>349</v>
+        <v>379</v>
       </c>
       <c r="D49" t="s">
         <v>15</v>
       </c>
       <c r="E49" t="s">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="F49" t="s">
-        <v>351</v>
+        <v>381</v>
       </c>
       <c r="G49" t="s">
-        <v>352</v>
+        <v>382</v>
       </c>
       <c r="H49" t="s">
-        <v>353</v>
+        <v>383</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -3634,22 +3634,22 @@
         <v>58</v>
       </c>
       <c r="C50" t="s">
-        <v>427</v>
+        <v>384</v>
       </c>
       <c r="D50" t="s">
         <v>13</v>
       </c>
       <c r="E50" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="F50" t="s">
-        <v>355</v>
+        <v>386</v>
       </c>
       <c r="G50" t="s">
-        <v>356</v>
+        <v>387</v>
       </c>
       <c r="H50" t="s">
-        <v>357</v>
+        <v>388</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -3657,25 +3657,25 @@
         <v>38</v>
       </c>
       <c r="B51" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C51" t="s">
-        <v>358</v>
+        <v>389</v>
       </c>
       <c r="D51" t="s">
         <v>13</v>
       </c>
       <c r="E51" t="s">
-        <v>359</v>
+        <v>390</v>
       </c>
       <c r="F51" t="s">
-        <v>360</v>
+        <v>391</v>
       </c>
       <c r="G51" t="s">
-        <v>361</v>
+        <v>392</v>
       </c>
       <c r="H51" t="s">
-        <v>362</v>
+        <v>393</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -3686,22 +3686,22 @@
         <v>58</v>
       </c>
       <c r="C52" t="s">
-        <v>438</v>
+        <v>394</v>
       </c>
       <c r="D52" t="s">
         <v>14</v>
       </c>
       <c r="E52" t="s">
-        <v>363</v>
+        <v>395</v>
       </c>
       <c r="F52" t="s">
-        <v>364</v>
+        <v>396</v>
       </c>
       <c r="G52" t="s">
-        <v>365</v>
+        <v>397</v>
       </c>
       <c r="H52" t="s">
-        <v>366</v>
+        <v>398</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -3709,25 +3709,25 @@
         <v>39</v>
       </c>
       <c r="B53" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C53" t="s">
-        <v>367</v>
+        <v>399</v>
       </c>
       <c r="D53" t="s">
         <v>14</v>
       </c>
       <c r="E53" t="s">
-        <v>368</v>
+        <v>400</v>
       </c>
       <c r="F53" t="s">
-        <v>369</v>
+        <v>401</v>
       </c>
       <c r="G53" t="s">
-        <v>370</v>
+        <v>402</v>
       </c>
       <c r="H53" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -3738,22 +3738,22 @@
         <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="D54" t="s">
         <v>13</v>
       </c>
       <c r="E54" t="s">
-        <v>372</v>
+        <v>405</v>
       </c>
       <c r="F54" t="s">
-        <v>373</v>
+        <v>406</v>
       </c>
       <c r="G54" t="s">
-        <v>374</v>
+        <v>407</v>
       </c>
       <c r="H54" t="s">
-        <v>375</v>
+        <v>408</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -3764,22 +3764,22 @@
         <v>58</v>
       </c>
       <c r="C55" t="s">
-        <v>439</v>
+        <v>409</v>
       </c>
       <c r="D55" t="s">
         <v>14</v>
       </c>
       <c r="E55" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
       <c r="F55" t="s">
-        <v>377</v>
+        <v>411</v>
       </c>
       <c r="G55" t="s">
-        <v>378</v>
+        <v>412</v>
       </c>
       <c r="H55" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -3787,25 +3787,25 @@
         <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C56" t="s">
-        <v>380</v>
+        <v>414</v>
       </c>
       <c r="D56" t="s">
         <v>13</v>
       </c>
       <c r="E56" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="F56" t="s">
-        <v>382</v>
+        <v>416</v>
       </c>
       <c r="G56" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="H56" t="s">
-        <v>384</v>
+        <v>418</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
@@ -3813,25 +3813,25 @@
         <v>40</v>
       </c>
       <c r="B57" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C57" t="s">
-        <v>385</v>
+        <v>419</v>
       </c>
       <c r="D57" t="s">
         <v>14</v>
       </c>
       <c r="E57" t="s">
-        <v>386</v>
+        <v>420</v>
       </c>
       <c r="F57" t="s">
-        <v>387</v>
+        <v>421</v>
       </c>
       <c r="G57" t="s">
-        <v>388</v>
+        <v>422</v>
       </c>
       <c r="H57" t="s">
-        <v>389</v>
+        <v>423</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -3842,22 +3842,22 @@
         <v>58</v>
       </c>
       <c r="C58" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="D58" t="s">
         <v>13</v>
       </c>
       <c r="E58" t="s">
-        <v>390</v>
+        <v>425</v>
       </c>
       <c r="F58" t="s">
-        <v>391</v>
+        <v>426</v>
       </c>
       <c r="G58" t="s">
-        <v>392</v>
+        <v>427</v>
       </c>
       <c r="H58" t="s">
-        <v>393</v>
+        <v>428</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -3865,25 +3865,25 @@
         <v>41</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C59" t="s">
-        <v>394</v>
+        <v>429</v>
       </c>
       <c r="D59" t="s">
         <v>13</v>
       </c>
       <c r="E59" t="s">
-        <v>395</v>
+        <v>430</v>
       </c>
       <c r="F59" t="s">
-        <v>396</v>
+        <v>431</v>
       </c>
       <c r="G59" t="s">
-        <v>397</v>
+        <v>432</v>
       </c>
       <c r="H59" t="s">
-        <v>398</v>
+        <v>433</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -3894,22 +3894,22 @@
         <v>58</v>
       </c>
       <c r="C60" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="D60" t="s">
         <v>13</v>
       </c>
       <c r="E60" t="s">
-        <v>399</v>
+        <v>435</v>
       </c>
       <c r="F60" t="s">
-        <v>400</v>
+        <v>436</v>
       </c>
       <c r="G60" t="s">
-        <v>401</v>
+        <v>437</v>
       </c>
       <c r="H60" t="s">
-        <v>402</v>
+        <v>438</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -3917,25 +3917,25 @@
         <v>42</v>
       </c>
       <c r="B61" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C61" t="s">
-        <v>403</v>
+        <v>439</v>
       </c>
       <c r="D61" t="s">
         <v>13</v>
       </c>
       <c r="E61" t="s">
-        <v>404</v>
+        <v>440</v>
       </c>
       <c r="F61" t="s">
-        <v>405</v>
+        <v>441</v>
       </c>
       <c r="G61" t="s">
-        <v>406</v>
+        <v>442</v>
       </c>
       <c r="H61" t="s">
-        <v>407</v>
+        <v>443</v>
       </c>
     </row>
   </sheetData>
